--- a/perplexity_examples/instrument_volatility_analysis.xlsx
+++ b/perplexity_examples/instrument_volatility_analysis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="249">
   <si>
     <t>System_Used_Vol_Annual</t>
   </si>
@@ -99,12 +99,12 @@
     <t>EMHY</t>
   </si>
   <si>
+    <t>VMBS</t>
+  </si>
+  <si>
     <t>VWOB</t>
   </si>
   <si>
-    <t>VMBS</t>
-  </si>
-  <si>
     <t>EMB</t>
   </si>
   <si>
@@ -138,12 +138,12 @@
     <t>FLCA</t>
   </si>
   <si>
+    <t>SPTL</t>
+  </si>
+  <si>
     <t>IEMG</t>
   </si>
   <si>
-    <t>SPTL</t>
-  </si>
-  <si>
     <t>KSA</t>
   </si>
   <si>
@@ -174,367 +174,367 @@
     <t>1.76%</t>
   </si>
   <si>
-    <t>1.79%</t>
-  </si>
-  <si>
-    <t>3.49%</t>
-  </si>
-  <si>
-    <t>3.56%</t>
-  </si>
-  <si>
-    <t>3.99%</t>
+    <t>1.81%</t>
+  </si>
+  <si>
+    <t>3.50%</t>
+  </si>
+  <si>
+    <t>3.69%</t>
+  </si>
+  <si>
+    <t>3.91%</t>
   </si>
   <si>
     <t>4.25%</t>
   </si>
   <si>
-    <t>4.44%</t>
+    <t>4.52%</t>
   </si>
   <si>
     <t>4.55%</t>
   </si>
   <si>
+    <t>4.77%</t>
+  </si>
+  <si>
+    <t>4.85%</t>
+  </si>
+  <si>
+    <t>4.94%</t>
+  </si>
+  <si>
+    <t>5.18%</t>
+  </si>
+  <si>
+    <t>5.56%</t>
+  </si>
+  <si>
+    <t>6.07%</t>
+  </si>
+  <si>
+    <t>6.47%</t>
+  </si>
+  <si>
+    <t>7.75%</t>
+  </si>
+  <si>
+    <t>8.36%</t>
+  </si>
+  <si>
+    <t>8.60%</t>
+  </si>
+  <si>
+    <t>8.80%</t>
+  </si>
+  <si>
+    <t>8.94%</t>
+  </si>
+  <si>
+    <t>11.01%</t>
+  </si>
+  <si>
+    <t>11.21%</t>
+  </si>
+  <si>
+    <t>12.15%</t>
+  </si>
+  <si>
+    <t>12.17%</t>
+  </si>
+  <si>
+    <t>12.22%</t>
+  </si>
+  <si>
+    <t>12.47%</t>
+  </si>
+  <si>
+    <t>12.82%</t>
+  </si>
+  <si>
+    <t>13.73%</t>
+  </si>
+  <si>
+    <t>15.56%</t>
+  </si>
+  <si>
+    <t>17.78%</t>
+  </si>
+  <si>
+    <t>19.00%</t>
+  </si>
+  <si>
+    <t>21.45%</t>
+  </si>
+  <si>
+    <t>1.66%</t>
+  </si>
+  <si>
+    <t>3.38%</t>
+  </si>
+  <si>
+    <t>8.18%</t>
+  </si>
+  <si>
+    <t>8.78%</t>
+  </si>
+  <si>
+    <t>6.13%</t>
+  </si>
+  <si>
     <t>4.73%</t>
   </si>
   <si>
-    <t>4.80%</t>
-  </si>
-  <si>
-    <t>5.05%</t>
-  </si>
-  <si>
-    <t>5.91%</t>
-  </si>
-  <si>
-    <t>6.05%</t>
-  </si>
-  <si>
-    <t>6.56%</t>
-  </si>
-  <si>
-    <t>7.82%</t>
+    <t>5.97%</t>
+  </si>
+  <si>
+    <t>6.75%</t>
+  </si>
+  <si>
+    <t>11.58%</t>
+  </si>
+  <si>
+    <t>5.82%</t>
+  </si>
+  <si>
+    <t>10.08%</t>
+  </si>
+  <si>
+    <t>10.70%</t>
+  </si>
+  <si>
+    <t>14.44%</t>
+  </si>
+  <si>
+    <t>10.10%</t>
+  </si>
+  <si>
+    <t>10.33%</t>
+  </si>
+  <si>
+    <t>16.26%</t>
+  </si>
+  <si>
+    <t>8.88%</t>
+  </si>
+  <si>
+    <t>10.53%</t>
+  </si>
+  <si>
+    <t>13.80%</t>
+  </si>
+  <si>
+    <t>19.77%</t>
+  </si>
+  <si>
+    <t>19.24%</t>
+  </si>
+  <si>
+    <t>14.69%</t>
+  </si>
+  <si>
+    <t>20.40%</t>
+  </si>
+  <si>
+    <t>20.48%</t>
+  </si>
+  <si>
+    <t>19.55%</t>
+  </si>
+  <si>
+    <t>14.43%</t>
+  </si>
+  <si>
+    <t>17.44%</t>
+  </si>
+  <si>
+    <t>29.05%</t>
+  </si>
+  <si>
+    <t>31.18%</t>
+  </si>
+  <si>
+    <t>28.67%</t>
+  </si>
+  <si>
+    <t>1.83%</t>
+  </si>
+  <si>
+    <t>1.78%</t>
+  </si>
+  <si>
+    <t>2.68%</t>
+  </si>
+  <si>
+    <t>2.73%</t>
+  </si>
+  <si>
+    <t>4.12%</t>
+  </si>
+  <si>
+    <t>4.29%</t>
+  </si>
+  <si>
+    <t>3.93%</t>
+  </si>
+  <si>
+    <t>4.64%</t>
+  </si>
+  <si>
+    <t>4.31%</t>
+  </si>
+  <si>
+    <t>4.50%</t>
+  </si>
+  <si>
+    <t>5.61%</t>
+  </si>
+  <si>
+    <t>4.76%</t>
+  </si>
+  <si>
+    <t>5.90%</t>
+  </si>
+  <si>
+    <t>7.31%</t>
+  </si>
+  <si>
+    <t>7.22%</t>
   </si>
   <si>
     <t>8.56%</t>
   </si>
   <si>
-    <t>8.69%</t>
-  </si>
-  <si>
-    <t>8.79%</t>
-  </si>
-  <si>
-    <t>8.85%</t>
-  </si>
-  <si>
-    <t>11.05%</t>
-  </si>
-  <si>
-    <t>11.47%</t>
-  </si>
-  <si>
-    <t>11.63%</t>
-  </si>
-  <si>
-    <t>11.80%</t>
-  </si>
-  <si>
-    <t>12.86%</t>
-  </si>
-  <si>
-    <t>13.30%</t>
-  </si>
-  <si>
-    <t>13.54%</t>
-  </si>
-  <si>
-    <t>13.75%</t>
-  </si>
-  <si>
-    <t>15.80%</t>
-  </si>
-  <si>
-    <t>17.89%</t>
-  </si>
-  <si>
-    <t>19.12%</t>
-  </si>
-  <si>
-    <t>21.00%</t>
-  </si>
-  <si>
-    <t>1.66%</t>
-  </si>
-  <si>
-    <t>3.38%</t>
-  </si>
-  <si>
-    <t>8.18%</t>
-  </si>
-  <si>
-    <t>6.13%</t>
-  </si>
-  <si>
-    <t>5.97%</t>
-  </si>
-  <si>
-    <t>6.76%</t>
-  </si>
-  <si>
-    <t>11.59%</t>
-  </si>
-  <si>
-    <t>10.09%</t>
-  </si>
-  <si>
-    <t>5.82%</t>
+    <t>8.15%</t>
+  </si>
+  <si>
+    <t>8.19%</t>
   </si>
   <si>
     <t>10.71%</t>
   </si>
   <si>
-    <t>14.45%</t>
-  </si>
-  <si>
-    <t>10.11%</t>
-  </si>
-  <si>
-    <t>10.34%</t>
-  </si>
-  <si>
-    <t>16.27%</t>
-  </si>
-  <si>
-    <t>8.88%</t>
-  </si>
-  <si>
-    <t>10.53%</t>
-  </si>
-  <si>
-    <t>13.81%</t>
-  </si>
-  <si>
-    <t>19.78%</t>
-  </si>
-  <si>
-    <t>19.25%</t>
-  </si>
-  <si>
-    <t>20.41%</t>
-  </si>
-  <si>
-    <t>14.70%</t>
-  </si>
-  <si>
-    <t>20.49%</t>
+    <t>10.99%</t>
+  </si>
+  <si>
+    <t>10.49%</t>
+  </si>
+  <si>
+    <t>10.81%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>13.37%</t>
+  </si>
+  <si>
+    <t>9.47%</t>
+  </si>
+  <si>
+    <t>20.38%</t>
+  </si>
+  <si>
+    <t>17.29%</t>
+  </si>
+  <si>
+    <t>19.89%</t>
+  </si>
+  <si>
+    <t>23.44%</t>
+  </si>
+  <si>
+    <t>1.68%</t>
+  </si>
+  <si>
+    <t>1.58%</t>
+  </si>
+  <si>
+    <t>5.45%</t>
+  </si>
+  <si>
+    <t>5.50%</t>
+  </si>
+  <si>
+    <t>4.60%</t>
+  </si>
+  <si>
+    <t>4.33%</t>
+  </si>
+  <si>
+    <t>5.28%</t>
+  </si>
+  <si>
+    <t>7.09%</t>
+  </si>
+  <si>
+    <t>5.52%</t>
+  </si>
+  <si>
+    <t>6.59%</t>
+  </si>
+  <si>
+    <t>7.06%</t>
+  </si>
+  <si>
+    <t>6.35%</t>
+  </si>
+  <si>
+    <t>6.33%</t>
+  </si>
+  <si>
+    <t>7.29%</t>
+  </si>
+  <si>
+    <t>8.38%</t>
+  </si>
+  <si>
+    <t>10.37%</t>
+  </si>
+  <si>
+    <t>8.98%</t>
+  </si>
+  <si>
+    <t>9.98%</t>
+  </si>
+  <si>
+    <t>11.10%</t>
+  </si>
+  <si>
+    <t>18.66%</t>
+  </si>
+  <si>
+    <t>15.74%</t>
+  </si>
+  <si>
+    <t>11.99%</t>
+  </si>
+  <si>
+    <t>17.96%</t>
+  </si>
+  <si>
+    <t>13.97%</t>
+  </si>
+  <si>
+    <t>17.16%</t>
+  </si>
+  <si>
+    <t>17.22%</t>
+  </si>
+  <si>
+    <t>18.85%</t>
   </si>
   <si>
     <t>19.56%</t>
   </si>
   <si>
-    <t>14.44%</t>
-  </si>
-  <si>
-    <t>19.57%</t>
-  </si>
-  <si>
-    <t>17.44%</t>
-  </si>
-  <si>
-    <t>29.07%</t>
-  </si>
-  <si>
-    <t>31.19%</t>
-  </si>
-  <si>
-    <t>28.68%</t>
-  </si>
-  <si>
-    <t>1.69%</t>
-  </si>
-  <si>
-    <t>2.59%</t>
-  </si>
-  <si>
-    <t>2.48%</t>
-  </si>
-  <si>
-    <t>3.84%</t>
-  </si>
-  <si>
-    <t>4.00%</t>
-  </si>
-  <si>
-    <t>3.88%</t>
-  </si>
-  <si>
-    <t>4.12%</t>
-  </si>
-  <si>
-    <t>3.90%</t>
-  </si>
-  <si>
-    <t>4.03%</t>
-  </si>
-  <si>
-    <t>4.45%</t>
-  </si>
-  <si>
-    <t>4.26%</t>
-  </si>
-  <si>
-    <t>5.60%</t>
-  </si>
-  <si>
-    <t>5.74%</t>
-  </si>
-  <si>
-    <t>7.23%</t>
-  </si>
-  <si>
-    <t>7.17%</t>
-  </si>
-  <si>
-    <t>8.24%</t>
-  </si>
-  <si>
-    <t>8.27%</t>
-  </si>
-  <si>
-    <t>7.87%</t>
-  </si>
-  <si>
-    <t>10.47%</t>
-  </si>
-  <si>
-    <t>10.93%</t>
-  </si>
-  <si>
-    <t>9.86%</t>
-  </si>
-  <si>
-    <t>10.02%</t>
-  </si>
-  <si>
-    <t>10.29%</t>
-  </si>
-  <si>
-    <t>13.58%</t>
-  </si>
-  <si>
-    <t>13.50%</t>
-  </si>
-  <si>
-    <t>9.63%</t>
-  </si>
-  <si>
-    <t>19.70%</t>
-  </si>
-  <si>
-    <t>16.95%</t>
-  </si>
-  <si>
-    <t>19.17%</t>
-  </si>
-  <si>
-    <t>22.89%</t>
-  </si>
-  <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>1.57%</t>
-  </si>
-  <si>
-    <t>5.44%</t>
-  </si>
-  <si>
-    <t>5.49%</t>
-  </si>
-  <si>
-    <t>4.62%</t>
-  </si>
-  <si>
-    <t>4.30%</t>
-  </si>
-  <si>
-    <t>4.57%</t>
-  </si>
-  <si>
-    <t>5.26%</t>
-  </si>
-  <si>
-    <t>7.08%</t>
-  </si>
-  <si>
-    <t>6.58%</t>
-  </si>
-  <si>
-    <t>5.50%</t>
-  </si>
-  <si>
-    <t>7.05%</t>
-  </si>
-  <si>
-    <t>6.36%</t>
-  </si>
-  <si>
-    <t>6.33%</t>
-  </si>
-  <si>
-    <t>7.29%</t>
-  </si>
-  <si>
-    <t>8.40%</t>
-  </si>
-  <si>
-    <t>10.37%</t>
-  </si>
-  <si>
-    <t>8.96%</t>
-  </si>
-  <si>
-    <t>9.97%</t>
-  </si>
-  <si>
-    <t>11.07%</t>
-  </si>
-  <si>
-    <t>18.64%</t>
-  </si>
-  <si>
-    <t>15.73%</t>
-  </si>
-  <si>
-    <t>17.94%</t>
-  </si>
-  <si>
-    <t>11.92%</t>
-  </si>
-  <si>
-    <t>13.98%</t>
-  </si>
-  <si>
-    <t>17.16%</t>
-  </si>
-  <si>
-    <t>17.23%</t>
-  </si>
-  <si>
-    <t>18.86%</t>
-  </si>
-  <si>
-    <t>19.54%</t>
-  </si>
-  <si>
-    <t>20.47%</t>
+    <t>20.50%</t>
   </si>
   <si>
     <t>24.10%</t>
   </si>
   <si>
-    <t>28.57%</t>
+    <t>28.60%</t>
   </si>
   <si>
     <t>0.10%</t>
@@ -543,36 +543,39 @@
     <t>0.21%</t>
   </si>
   <si>
+    <t>0.51%</t>
+  </si>
+  <si>
+    <t>0.55%</t>
+  </si>
+  <si>
+    <t>0.39%</t>
+  </si>
+  <si>
+    <t>0.30%</t>
+  </si>
+  <si>
+    <t>0.38%</t>
+  </si>
+  <si>
+    <t>0.43%</t>
+  </si>
+  <si>
+    <t>0.73%</t>
+  </si>
+  <si>
+    <t>0.37%</t>
+  </si>
+  <si>
+    <t>0.64%</t>
+  </si>
+  <si>
+    <t>0.67%</t>
+  </si>
+  <si>
     <t>0.52%</t>
   </si>
   <si>
-    <t>0.55%</t>
-  </si>
-  <si>
-    <t>0.39%</t>
-  </si>
-  <si>
-    <t>0.30%</t>
-  </si>
-  <si>
-    <t>0.38%</t>
-  </si>
-  <si>
-    <t>0.43%</t>
-  </si>
-  <si>
-    <t>0.73%</t>
-  </si>
-  <si>
-    <t>0.64%</t>
-  </si>
-  <si>
-    <t>0.37%</t>
-  </si>
-  <si>
-    <t>0.67%</t>
-  </si>
-  <si>
     <t>0.91%</t>
   </si>
   <si>
@@ -597,27 +600,24 @@
     <t>1.21%</t>
   </si>
   <si>
+    <t>0.93%</t>
+  </si>
+  <si>
+    <t>1.28%</t>
+  </si>
+  <si>
     <t>1.29%</t>
   </si>
   <si>
-    <t>0.93%</t>
-  </si>
-  <si>
     <t>1.23%</t>
   </si>
   <si>
     <t>1.10%</t>
   </si>
   <si>
-    <t>1.83%</t>
-  </si>
-  <si>
     <t>1.96%</t>
   </si>
   <si>
-    <t>1.81%</t>
-  </si>
-  <si>
     <t>12.00%</t>
   </si>
   <si>
@@ -642,94 +642,97 @@
     <t>Explanation</t>
   </si>
   <si>
-    <t>NORMAL_VOL: 11.1% vol close to 12% target, scaling 1.09x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.7% vol close to 12% target, scaling 1.38x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.0% vol needs 3.0x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 5.1% vol needs 2.4x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.7% vol needs 2.5x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 6.6% vol close to 12% target, scaling 1.83x</t>
-  </si>
-  <si>
-    <t>HIGH_VOL: 21.0% vol needs 0.57x less capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>HIGH_VOL: 19.1% vol needs 0.63x less capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 11.5% vol close to 12% target, scaling 1.05x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 15.8% vol close to 12% target, scaling 0.76x</t>
+    <t>NORMAL_VOL: 11.0% vol close to 12% target, scaling 1.09x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 8.6% vol close to 12% target, scaling 1.40x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 3.9% vol needs 3.1x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 5.2% vol needs 2.3x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.8% vol needs 2.5x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 6.5% vol close to 12% target, scaling 1.85x</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 21.4% vol needs 0.56x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 19.0% vol needs 0.63x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 11.2% vol close to 12% target, scaling 1.07x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 15.6% vol close to 12% target, scaling 0.77x</t>
   </si>
   <si>
     <t>NORMAL_VOL: 6.1% vol close to 12% target, scaling 1.98x</t>
   </si>
   <si>
-    <t>LOW_VOL: 3.6% vol needs 3.4x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 13.5% vol close to 12% target, scaling 0.89x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.6% vol close to 12% target, scaling 1.40x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 11.6% vol close to 12% target, scaling 1.03x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 5.9% vol needs 2.0x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 17.9% vol close to 12% target, scaling 0.67x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 13.8% vol close to 12% target, scaling 0.87x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 12.9% vol close to 12% target, scaling 0.93x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 7.8% vol close to 12% target, scaling 1.53x</t>
+    <t>LOW_VOL: 3.7% vol needs 3.2x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 12.8% vol close to 12% target, scaling 0.94x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 8.4% vol close to 12% target, scaling 1.44x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 12.2% vol close to 12% target, scaling 0.99x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 5.6% vol needs 2.2x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 17.8% vol close to 12% target, scaling 0.68x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 13.7% vol close to 12% target, scaling 0.87x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 12.2% vol close to 12% target, scaling 0.98x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 7.7% vol close to 12% target, scaling 1.55x</t>
   </si>
   <si>
     <t>LOW_VOL: 1.8% vol needs 6.8x more capital to reach 12% target</t>
   </si>
   <si>
-    <t>LOW_VOL: 4.4% vol needs 2.7x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.2% vol needs 2.8x more capital to reach 12% target</t>
+    <t>LOW_VOL: 4.5% vol needs 2.7x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.3% vol needs 2.8x more capital to reach 12% target</t>
   </si>
   <si>
     <t>LOW_VOL: 3.5% vol needs 3.4x more capital to reach 12% target</t>
   </si>
   <si>
-    <t>LOW_VOL: 1.8% vol needs 6.7x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 11.8% vol close to 12% target, scaling 1.02x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.5% vol needs 2.6x more capital to reach 12% target</t>
+    <t>LOW_VOL: 1.8% vol needs 6.6x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.6% vol needs 2.6x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 8.9% vol close to 12% target, scaling 1.34x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 12.5% vol close to 12% target, scaling 0.96x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.9% vol needs 2.5x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.9% vol needs 2.4x more capital to reach 12% target</t>
   </si>
   <si>
     <t>NORMAL_VOL: 8.8% vol close to 12% target, scaling 1.36x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 13.3% vol close to 12% target, scaling 0.90x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.8% vol needs 2.5x more capital to reach 12% target</t>
   </si>
   <si>
     <t>Value</t>
@@ -1185,52 +1188,52 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>0.01763245787306867</v>
+        <v>0.01762469926214086</v>
       </c>
       <c r="C2">
-        <v>0.01659410234430448</v>
+        <v>0.01659809158636668</v>
       </c>
       <c r="D2">
-        <v>0.01793334487121786</v>
+        <v>0.01833460187285361</v>
       </c>
       <c r="E2">
-        <v>0.01668798307249646</v>
+        <v>0.01679016279081553</v>
       </c>
       <c r="F2">
-        <v>0.001045330191271038</v>
+        <v>0.001045581489899995</v>
       </c>
       <c r="G2">
         <v>0.12</v>
       </c>
       <c r="H2">
-        <v>6.805630891838662</v>
+        <v>6.808626814856849</v>
       </c>
       <c r="I2">
         <v>0.009096361455417834</v>
       </c>
       <c r="J2">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K2">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L2" t="s">
         <v>50</v>
       </c>
       <c r="M2">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N2" t="s">
         <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P2" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R2" t="s">
         <v>173</v>
@@ -1244,52 +1247,52 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>0.01791338682827996</v>
+        <v>0.01809404311665208</v>
       </c>
       <c r="C3">
-        <v>0.03382297834508645</v>
+        <v>0.03380599832475559</v>
       </c>
       <c r="D3">
-        <v>0.01691160179266494</v>
+        <v>0.0178006226272682</v>
       </c>
       <c r="E3">
-        <v>0.01566023151151356</v>
+        <v>0.01578008016422898</v>
       </c>
       <c r="F3">
-        <v>0.002130647364300517</v>
+        <v>0.002129577723561178</v>
       </c>
       <c r="G3">
         <v>0.12</v>
       </c>
       <c r="H3">
-        <v>6.69890072437644</v>
+        <v>6.632016914426557</v>
       </c>
       <c r="I3">
         <v>0.009096361455417834</v>
       </c>
       <c r="J3">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K3">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L3" t="s">
         <v>50</v>
       </c>
       <c r="M3">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N3" t="s">
         <v>52</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R3" t="s">
         <v>174</v>
@@ -1303,52 +1306,52 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>0.03490342407671233</v>
+        <v>0.03502611942537402</v>
       </c>
       <c r="C4">
-        <v>0.08180805827754846</v>
+        <v>0.08175352354600299</v>
       </c>
       <c r="D4">
-        <v>0.02590185554592101</v>
+        <v>0.02681095546290775</v>
       </c>
       <c r="E4">
-        <v>0.05443557781419659</v>
+        <v>0.05448797335121321</v>
       </c>
       <c r="F4">
-        <v>0.005153423272463625</v>
+        <v>0.005149987907285411</v>
       </c>
       <c r="G4">
         <v>0.12</v>
       </c>
       <c r="H4">
-        <v>3.438058103877103</v>
+        <v>3.426014698992554</v>
       </c>
       <c r="I4">
         <v>0.005497800879648141</v>
       </c>
       <c r="J4">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K4">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L4" t="s">
         <v>50</v>
       </c>
       <c r="M4">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N4" t="s">
         <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R4" t="s">
         <v>175</v>
@@ -1362,52 +1365,52 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>0.03563311718442798</v>
+        <v>0.03694532067208307</v>
       </c>
       <c r="C5">
-        <v>0.0878844158629722</v>
+        <v>0.08782984444390952</v>
       </c>
       <c r="D5">
-        <v>0.02475836320010139</v>
+        <v>0.02726544361215556</v>
       </c>
       <c r="E5">
-        <v>0.05490933660969859</v>
+        <v>0.05500660148161585</v>
       </c>
       <c r="F5">
-        <v>0.005536197821228676</v>
+        <v>0.005532760144954111</v>
       </c>
       <c r="G5">
         <v>0.12</v>
       </c>
       <c r="H5">
-        <v>3.367653730065501</v>
+        <v>3.248043265481125</v>
       </c>
       <c r="I5">
         <v>0.005497800879648141</v>
       </c>
       <c r="J5">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K5">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L5" t="s">
         <v>50</v>
       </c>
       <c r="M5">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N5" t="s">
         <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="P5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R5" t="s">
         <v>176</v>
@@ -1421,52 +1424,52 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>0.03988905080476223</v>
+        <v>0.03914619504344222</v>
       </c>
       <c r="C6">
-        <v>0.06131587861704697</v>
+        <v>0.06127978794129803</v>
       </c>
       <c r="D6">
-        <v>0.03838427178573873</v>
+        <v>0.03906767639849132</v>
       </c>
       <c r="E6">
-        <v>0.04621767080098219</v>
+        <v>0.04603199891185989</v>
       </c>
       <c r="F6">
-        <v>0.00386253729143165</v>
+        <v>0.003860263792558318</v>
       </c>
       <c r="G6">
         <v>0.12</v>
       </c>
       <c r="H6">
-        <v>3.008344334572974</v>
+        <v>3.065432026454444</v>
       </c>
       <c r="I6">
         <v>0.005497800879648141</v>
       </c>
       <c r="J6">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K6">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L6" t="s">
         <v>50</v>
       </c>
       <c r="M6">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N6" t="s">
         <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R6" t="s">
         <v>177</v>
@@ -1480,52 +1483,52 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>0.04249235515673782</v>
+        <v>0.0425423662168037</v>
       </c>
       <c r="C7">
-        <v>0.04726119404132093</v>
+        <v>0.04725179619000613</v>
       </c>
       <c r="D7">
-        <v>0.03997311826187686</v>
+        <v>0.04115602548720683</v>
       </c>
       <c r="E7">
-        <v>0.04304664924058597</v>
+        <v>0.04326591465460872</v>
       </c>
       <c r="F7">
-        <v>0.002977175383269116</v>
+        <v>0.002976583374282513</v>
       </c>
       <c r="G7">
         <v>0.12</v>
       </c>
       <c r="H7">
-        <v>2.824037395841358</v>
+        <v>2.820717573358708</v>
       </c>
       <c r="I7">
         <v>0.009096361455417834</v>
       </c>
       <c r="J7">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K7">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L7" t="s">
         <v>50</v>
       </c>
       <c r="M7">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N7" t="s">
         <v>56</v>
       </c>
       <c r="O7" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="P7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R7" t="s">
         <v>178</v>
@@ -1539,52 +1542,52 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>0.04435880841436476</v>
+        <v>0.04523816926953131</v>
       </c>
       <c r="C8">
-        <v>0.05970350441783935</v>
+        <v>0.05968642054957227</v>
       </c>
       <c r="D8">
-        <v>0.03880103328275212</v>
+        <v>0.04124612217863163</v>
       </c>
       <c r="E8">
-        <v>0.04567766280210517</v>
+        <v>0.04596450143136226</v>
       </c>
       <c r="F8">
-        <v>0.003760967264015453</v>
+        <v>0.003759891081471032</v>
       </c>
       <c r="G8">
         <v>0.12</v>
       </c>
       <c r="H8">
-        <v>2.705212432197351</v>
+        <v>2.652627237964337</v>
       </c>
       <c r="I8">
         <v>0.01009596161535386</v>
       </c>
       <c r="J8">
-        <v>0.0100959616154199</v>
+        <v>0.0100959616154168</v>
       </c>
       <c r="K8">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L8" t="s">
         <v>50</v>
       </c>
       <c r="M8">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N8" t="s">
         <v>57</v>
       </c>
       <c r="O8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R8" t="s">
         <v>179</v>
@@ -1598,49 +1601,49 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>0.04548321420369619</v>
+        <v>0.04551625614122628</v>
       </c>
       <c r="C9">
-        <v>0.06756682138017417</v>
+        <v>0.06753532939207312</v>
       </c>
       <c r="D9">
-        <v>0.04117583381799126</v>
+        <v>0.04286117691899444</v>
       </c>
       <c r="E9">
-        <v>0.05261533971500426</v>
+        <v>0.05278748843208499</v>
       </c>
       <c r="F9">
-        <v>0.004256309672644352</v>
+        <v>0.004254325863863248</v>
       </c>
       <c r="G9">
         <v>0.12</v>
       </c>
       <c r="H9">
-        <v>2.638335968574714</v>
+        <v>2.636420702697254</v>
       </c>
       <c r="I9">
         <v>0.009096361455417834</v>
       </c>
       <c r="J9">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K9">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L9" t="s">
         <v>50</v>
       </c>
       <c r="M9">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N9" t="s">
         <v>58</v>
       </c>
       <c r="O9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q9" t="s">
         <v>148</v>
@@ -1657,49 +1660,49 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>0.0473013380209173</v>
+        <v>0.04770117265223589</v>
       </c>
       <c r="C10">
-        <v>0.1158895255163199</v>
+        <v>0.1158112727183454</v>
       </c>
       <c r="D10">
-        <v>0.03895118676153349</v>
+        <v>0.03925305962803242</v>
       </c>
       <c r="E10">
-        <v>0.07082979686888019</v>
+        <v>0.07088242212865427</v>
       </c>
       <c r="F10">
-        <v>0.007300353906510875</v>
+        <v>0.007295424443586221</v>
       </c>
       <c r="G10">
         <v>0.12</v>
       </c>
       <c r="H10">
-        <v>2.536926121348499</v>
+        <v>2.515661425660471</v>
       </c>
       <c r="I10">
         <v>0.01859256297481008</v>
       </c>
       <c r="J10">
-        <v>0.01859256297493169</v>
+        <v>0.01859256297492599</v>
       </c>
       <c r="K10">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L10" t="s">
         <v>50</v>
       </c>
       <c r="M10">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N10" t="s">
         <v>59</v>
       </c>
       <c r="O10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="s">
         <v>149</v>
@@ -1716,49 +1719,49 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.04796765594392619</v>
+        <v>0.04853638764815744</v>
       </c>
       <c r="C11">
-        <v>0.1009006228681098</v>
+        <v>0.05820630130771236</v>
       </c>
       <c r="D11">
-        <v>0.04029876080882771</v>
+        <v>0.04643763892460204</v>
       </c>
       <c r="E11">
-        <v>0.06581434266631514</v>
+        <v>0.05523233757399295</v>
       </c>
       <c r="F11">
-        <v>0.006356141791441317</v>
+        <v>0.003666652333264299</v>
       </c>
       <c r="G11">
         <v>0.12</v>
       </c>
       <c r="H11">
-        <v>2.50168572215159</v>
+        <v>2.472371880451542</v>
       </c>
       <c r="I11">
-        <v>0.02479008396641344</v>
+        <v>0.007297081167532987</v>
       </c>
       <c r="J11">
-        <v>0.02479008396657559</v>
+        <v>0.007297081167578481</v>
       </c>
       <c r="K11">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L11" t="s">
         <v>50</v>
       </c>
       <c r="M11">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N11" t="s">
         <v>60</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="P11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="s">
         <v>150</v>
@@ -1775,49 +1778,49 @@
         <v>28</v>
       </c>
       <c r="B12">
-        <v>0.04803882356860375</v>
+        <v>0.04935812195542288</v>
       </c>
       <c r="C12">
-        <v>0.05821713028335997</v>
+        <v>0.1008416194848006</v>
       </c>
       <c r="D12">
-        <v>0.04445592878335218</v>
+        <v>0.04306628604415293</v>
       </c>
       <c r="E12">
-        <v>0.05496098821754505</v>
+        <v>0.06594999924372404</v>
       </c>
       <c r="F12">
-        <v>0.003667334494609946</v>
+        <v>0.006352424927661615</v>
       </c>
       <c r="G12">
         <v>0.12</v>
       </c>
       <c r="H12">
-        <v>2.497979573305521</v>
+        <v>2.431210816902158</v>
       </c>
       <c r="I12">
-        <v>0.007297081167532987</v>
+        <v>0.02479008396641344</v>
       </c>
       <c r="J12">
-        <v>0.007297081167580719</v>
+        <v>0.02479008396656799</v>
       </c>
       <c r="K12">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L12" t="s">
         <v>50</v>
       </c>
       <c r="M12">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q12" t="s">
         <v>151</v>
@@ -1834,49 +1837,49 @@
         <v>29</v>
       </c>
       <c r="B13">
-        <v>0.05052690389806113</v>
+        <v>0.05181018488653797</v>
       </c>
       <c r="C13">
-        <v>0.1070642266893728</v>
+        <v>0.1070007691823626</v>
       </c>
       <c r="D13">
-        <v>0.04261051292742499</v>
+        <v>0.04504281680683247</v>
       </c>
       <c r="E13">
-        <v>0.07047308788223361</v>
+        <v>0.07059593803018702</v>
       </c>
       <c r="F13">
-        <v>0.006744412336464871</v>
+        <v>0.006740414889265607</v>
       </c>
       <c r="G13">
         <v>0.12</v>
       </c>
       <c r="H13">
-        <v>2.374972356155089</v>
+        <v>2.316146917112817</v>
       </c>
       <c r="I13">
         <v>0.0505797680927629</v>
       </c>
       <c r="J13">
-        <v>0.05057976809309375</v>
+        <v>0.05057976809307824</v>
       </c>
       <c r="K13">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L13" t="s">
         <v>50</v>
       </c>
       <c r="M13">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q13" t="s">
         <v>152</v>
@@ -1893,55 +1896,55 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>0.05905167052056143</v>
+        <v>0.05563680009278063</v>
       </c>
       <c r="C14">
-        <v>0.08184425801267448</v>
+        <v>0.08178553433194409</v>
       </c>
       <c r="D14">
-        <v>0.05604715884507699</v>
+        <v>0.05609307219061594</v>
       </c>
       <c r="E14">
-        <v>0.06358894948622108</v>
+        <v>0.06349039923138614</v>
       </c>
       <c r="F14">
-        <v>0.005155703641431955</v>
+        <v>0.005152004397258552</v>
       </c>
       <c r="G14">
         <v>0.12</v>
       </c>
       <c r="H14">
-        <v>2.032118633429967</v>
+        <v>2.156845825063384</v>
       </c>
       <c r="I14">
         <v>0.06377449020391843</v>
       </c>
       <c r="J14">
-        <v>0.06377449020433559</v>
+        <v>0.06377449020431604</v>
       </c>
       <c r="K14">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L14" t="s">
         <v>50</v>
       </c>
       <c r="M14">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q14" t="s">
         <v>153</v>
       </c>
       <c r="R14" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="S14" t="s">
         <v>200</v>
@@ -1952,55 +1955,55 @@
         <v>31</v>
       </c>
       <c r="B15">
-        <v>0.06053476212570217</v>
+        <v>0.06067006888567235</v>
       </c>
       <c r="C15">
-        <v>0.1444820530328741</v>
+        <v>0.144377250250269</v>
       </c>
       <c r="D15">
-        <v>0.04730950148813524</v>
+        <v>0.04764462380120212</v>
       </c>
       <c r="E15">
-        <v>0.06330401946612757</v>
+        <v>0.06327827101454939</v>
       </c>
       <c r="F15">
-        <v>0.009101513838976916</v>
+        <v>0.009094911884227376</v>
       </c>
       <c r="G15">
         <v>0.12</v>
       </c>
       <c r="H15">
-        <v>1.982332064852531</v>
+        <v>1.977911055715627</v>
       </c>
       <c r="I15">
         <v>0.007297081167532987</v>
       </c>
       <c r="J15">
-        <v>0.007297081167091044</v>
+        <v>0.007297081167111755</v>
       </c>
       <c r="K15">
-        <v>0.9999999999394356</v>
+        <v>0.999999999942274</v>
       </c>
       <c r="L15" t="s">
         <v>50</v>
       </c>
       <c r="M15">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="Q15" t="s">
         <v>154</v>
       </c>
       <c r="R15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S15" t="s">
         <v>200</v>
@@ -2011,55 +2014,55 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>0.06562669675920818</v>
+        <v>0.06469555905163277</v>
       </c>
       <c r="C16">
-        <v>0.1010947180793883</v>
+        <v>0.1010380446026012</v>
       </c>
       <c r="D16">
-        <v>0.05740792630564704</v>
+        <v>0.05901992590618146</v>
       </c>
       <c r="E16">
-        <v>0.07289260874875343</v>
+        <v>0.07287076127637157</v>
       </c>
       <c r="F16">
-        <v>0.006368368640482065</v>
+        <v>0.006364798547017493</v>
       </c>
       <c r="G16">
         <v>0.12</v>
       </c>
       <c r="H16">
-        <v>1.828524151387562</v>
+        <v>1.85484137951771</v>
       </c>
       <c r="I16">
         <v>0.01859256297481008</v>
       </c>
       <c r="J16">
-        <v>0.01859256297493169</v>
+        <v>0.01859256297492599</v>
       </c>
       <c r="K16">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L16" t="s">
         <v>50</v>
       </c>
       <c r="M16">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q16" t="s">
         <v>155</v>
       </c>
       <c r="R16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S16" t="s">
         <v>200</v>
@@ -2070,55 +2073,55 @@
         <v>33</v>
       </c>
       <c r="B17">
-        <v>0.07818290359200544</v>
+        <v>0.07745530214105066</v>
       </c>
       <c r="C17">
-        <v>0.1033702938267445</v>
+        <v>0.1033261756230675</v>
       </c>
       <c r="D17">
-        <v>0.0722754812201908</v>
+        <v>0.07314772014172524</v>
       </c>
       <c r="E17">
-        <v>0.08395533149510584</v>
+        <v>0.08383944071938246</v>
       </c>
       <c r="F17">
-        <v>0.006511716438505745</v>
+        <v>0.00650893725290526</v>
       </c>
       <c r="G17">
         <v>0.12</v>
       </c>
       <c r="H17">
-        <v>1.534862412199673</v>
+        <v>1.54928063906423</v>
       </c>
       <c r="I17">
         <v>0.06377449020391843</v>
       </c>
       <c r="J17">
-        <v>0.06377449020433559</v>
+        <v>0.06377449020431604</v>
       </c>
       <c r="K17">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L17" t="s">
         <v>50</v>
       </c>
       <c r="M17">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q17" t="s">
         <v>156</v>
       </c>
       <c r="R17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="S17" t="s">
         <v>200</v>
@@ -2129,55 +2132,55 @@
         <v>34</v>
       </c>
       <c r="B18">
-        <v>0.0856051699082177</v>
+        <v>0.08358202127746187</v>
       </c>
       <c r="C18">
-        <v>0.1626981643393582</v>
+        <v>0.1625931982412989</v>
       </c>
       <c r="D18">
-        <v>0.07171968771576304</v>
+        <v>0.07221056611840437</v>
       </c>
       <c r="E18">
-        <v>0.1036997462418575</v>
+        <v>0.1036988113042716</v>
       </c>
       <c r="F18">
-        <v>0.01024902099068236</v>
+        <v>0.01024240874802622</v>
       </c>
       <c r="G18">
         <v>0.12</v>
       </c>
       <c r="H18">
-        <v>1.401784496528177</v>
+        <v>1.435715458491291</v>
       </c>
       <c r="I18">
         <v>0.005497800879648141</v>
       </c>
       <c r="J18">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K18">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L18" t="s">
         <v>50</v>
       </c>
       <c r="M18">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q18" t="s">
         <v>157</v>
       </c>
       <c r="R18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S18" t="s">
         <v>200</v>
@@ -2188,55 +2191,55 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>0.08693937630280837</v>
+        <v>0.08599260288294111</v>
       </c>
       <c r="C19">
-        <v>0.08879661065980612</v>
+        <v>0.08877909105670397</v>
       </c>
       <c r="D19">
-        <v>0.0824202753847393</v>
+        <v>0.0855650189722526</v>
       </c>
       <c r="E19">
-        <v>0.08959337086054141</v>
+        <v>0.08975810484614052</v>
       </c>
       <c r="F19">
-        <v>0.005593660692173191</v>
+        <v>0.005592557060914219</v>
       </c>
       <c r="G19">
         <v>0.12</v>
       </c>
       <c r="H19">
-        <v>1.380272151735274</v>
+        <v>1.395468865657573</v>
       </c>
       <c r="I19">
         <v>0.08506597361055578</v>
       </c>
       <c r="J19">
-        <v>0.08506597361111221</v>
+        <v>0.08506597361108613</v>
       </c>
       <c r="K19">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L19" t="s">
         <v>50</v>
       </c>
       <c r="M19">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q19" t="s">
         <v>158</v>
       </c>
       <c r="R19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S19" t="s">
         <v>200</v>
@@ -2247,55 +2250,55 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>0.08793597123031011</v>
+        <v>0.08795103108520301</v>
       </c>
       <c r="C20">
-        <v>0.1053175895607682</v>
+        <v>0.1052790455646434</v>
       </c>
       <c r="D20">
-        <v>0.08269413281807082</v>
+        <v>0.08149139309562874</v>
       </c>
       <c r="E20">
-        <v>0.09968636253031758</v>
+        <v>0.09983301538084144</v>
       </c>
       <c r="F20">
-        <v>0.006634384539489638</v>
+        <v>0.006631956495959142</v>
       </c>
       <c r="G20">
         <v>0.12</v>
       </c>
       <c r="H20">
-        <v>1.364629267421316</v>
+        <v>1.364395601954335</v>
       </c>
       <c r="I20">
         <v>0.0235905637744902</v>
       </c>
       <c r="J20">
-        <v>0.02359056377464451</v>
+        <v>0.02359056377463728</v>
       </c>
       <c r="K20">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L20" t="s">
         <v>50</v>
       </c>
       <c r="M20">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q20" t="s">
         <v>159</v>
       </c>
       <c r="R20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S20" t="s">
         <v>200</v>
@@ -2306,55 +2309,55 @@
         <v>37</v>
       </c>
       <c r="B21">
-        <v>0.08847231604195015</v>
+        <v>0.0893857405791231</v>
       </c>
       <c r="C21">
-        <v>0.1380911305716999</v>
+        <v>0.1380233989343314</v>
       </c>
       <c r="D21">
-        <v>0.07872445222731052</v>
+        <v>0.08185506902534645</v>
       </c>
       <c r="E21">
-        <v>0.1107192425739013</v>
+        <v>0.1109874221455964</v>
       </c>
       <c r="F21">
-        <v>0.008698923565630155</v>
+        <v>0.008694656873526148</v>
       </c>
       <c r="G21">
         <v>0.12</v>
       </c>
       <c r="H21">
-        <v>1.356356489448074</v>
+        <v>1.342496009123262</v>
       </c>
       <c r="I21">
         <v>0.009096361455417834</v>
       </c>
       <c r="J21">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K21">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L21" t="s">
         <v>50</v>
       </c>
       <c r="M21">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q21" t="s">
         <v>160</v>
       </c>
       <c r="R21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S21" t="s">
         <v>200</v>
@@ -2365,55 +2368,55 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>0.1105449880348053</v>
+        <v>0.110051083502396</v>
       </c>
       <c r="C22">
-        <v>0.1978161304112204</v>
+        <v>0.197681324065112</v>
       </c>
       <c r="D22">
-        <v>0.1047411843081912</v>
+        <v>0.1070746296339144</v>
       </c>
       <c r="E22">
-        <v>0.1863965361969354</v>
+        <v>0.1865964815001218</v>
       </c>
       <c r="F22">
-        <v>0.01246124491393358</v>
+        <v>0.01245275291233939</v>
       </c>
       <c r="G22">
         <v>0.12</v>
       </c>
       <c r="H22">
-        <v>1.085530896816578</v>
+        <v>1.090402712821882</v>
       </c>
       <c r="I22">
         <v>0.06747301079568173</v>
       </c>
       <c r="J22">
-        <v>0.06747301079610854</v>
+        <v>0.0674730107960885</v>
       </c>
       <c r="K22">
-        <v>1.000000000006326</v>
+        <v>1.000000000006029</v>
       </c>
       <c r="L22" t="s">
         <v>50</v>
       </c>
       <c r="M22">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="N22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O22" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q22" t="s">
         <v>161</v>
       </c>
       <c r="R22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="S22" t="s">
         <v>200</v>
@@ -2424,55 +2427,55 @@
         <v>39</v>
       </c>
       <c r="B23">
-        <v>0.1147106489165815</v>
+        <v>0.1120818178495579</v>
       </c>
       <c r="C23">
-        <v>0.1924800025653199</v>
+        <v>0.1923590970756769</v>
       </c>
       <c r="D23">
-        <v>0.1092692647913903</v>
+        <v>0.1098680696991763</v>
       </c>
       <c r="E23">
-        <v>0.1572981003909255</v>
+        <v>0.1573947913173102</v>
       </c>
       <c r="F23">
-        <v>0.01212510045573597</v>
+        <v>0.01211748412578983</v>
       </c>
       <c r="G23">
         <v>0.12</v>
       </c>
       <c r="H23">
-        <v>1.046110375395618</v>
+        <v>1.070646446518831</v>
       </c>
       <c r="I23">
         <v>0.02249100359856058</v>
       </c>
       <c r="J23">
-        <v>0.02249100359870769</v>
+        <v>0.0224910035987008</v>
       </c>
       <c r="K23">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L23" t="s">
         <v>50</v>
       </c>
       <c r="M23">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q23" t="s">
         <v>162</v>
       </c>
       <c r="R23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S23" t="s">
         <v>200</v>
@@ -2483,55 +2486,55 @@
         <v>40</v>
       </c>
       <c r="B24">
-        <v>0.1163107796790405</v>
+        <v>0.1215164053503871</v>
       </c>
       <c r="C24">
-        <v>0.204056767616021</v>
+        <v>0.1469195459028001</v>
       </c>
       <c r="D24">
-        <v>0.09855146759552505</v>
+        <v>0.104903417863623</v>
       </c>
       <c r="E24">
-        <v>0.1793513107732368</v>
+        <v>0.1199080792781482</v>
       </c>
       <c r="F24">
-        <v>0.01285436810599262</v>
+        <v>0.009255061456984466</v>
       </c>
       <c r="G24">
         <v>0.12</v>
       </c>
       <c r="H24">
-        <v>1.031718644919585</v>
+        <v>0.9875209824877997</v>
       </c>
       <c r="I24">
-        <v>0.04498200719712115</v>
+        <v>0.009096361455417834</v>
       </c>
       <c r="J24">
-        <v>0.04498200719741539</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K24">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L24" t="s">
         <v>50</v>
       </c>
       <c r="M24">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q24" t="s">
         <v>163</v>
       </c>
       <c r="R24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S24" t="s">
         <v>200</v>
@@ -2542,55 +2545,55 @@
         <v>41</v>
       </c>
       <c r="B25">
-        <v>0.1179763332508383</v>
+        <v>0.1217349660257986</v>
       </c>
       <c r="C25">
-        <v>0.1469571374336077</v>
+        <v>0.2039807001655037</v>
       </c>
       <c r="D25">
-        <v>0.1002284265384976</v>
+        <v>0.1080689037661476</v>
       </c>
       <c r="E25">
-        <v>0.119235791813882</v>
+        <v>0.179605286423776</v>
       </c>
       <c r="F25">
-        <v>0.009257429500839688</v>
+        <v>0.01284957630701797</v>
       </c>
       <c r="G25">
         <v>0.12</v>
       </c>
       <c r="H25">
-        <v>1.017153158547986</v>
+        <v>0.985748005832351</v>
       </c>
       <c r="I25">
-        <v>0.009096361455417834</v>
+        <v>0.04498200719712115</v>
       </c>
       <c r="J25">
-        <v>0.009096361455477335</v>
+        <v>0.04498200719740159</v>
       </c>
       <c r="K25">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L25" t="s">
         <v>50</v>
       </c>
       <c r="M25">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q25" t="s">
         <v>164</v>
       </c>
       <c r="R25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="S25" t="s">
         <v>200</v>
@@ -2601,55 +2604,55 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>0.1286455579513547</v>
+        <v>0.1221898841733612</v>
       </c>
       <c r="C26">
-        <v>0.204938806680807</v>
+        <v>0.2047897038702714</v>
       </c>
       <c r="D26">
-        <v>0.1028800557413847</v>
+        <v>0.09543738975822265</v>
       </c>
       <c r="E26">
-        <v>0.1397784103941959</v>
+        <v>0.1396733077830793</v>
       </c>
       <c r="F26">
-        <v>0.01290993134437518</v>
+        <v>0.01290053875017381</v>
       </c>
       <c r="G26">
         <v>0.12</v>
       </c>
       <c r="H26">
-        <v>0.9327955190289281</v>
+        <v>0.9820780239855681</v>
       </c>
       <c r="I26">
         <v>0.01129548180727709</v>
       </c>
       <c r="J26">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="K26">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L26" t="s">
         <v>50</v>
       </c>
       <c r="M26">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q26" t="s">
         <v>165</v>
       </c>
       <c r="R26" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="S26" t="s">
         <v>200</v>
@@ -2660,55 +2663,55 @@
         <v>43</v>
       </c>
       <c r="B27">
-        <v>0.132967287498401</v>
+        <v>0.1246924739119454</v>
       </c>
       <c r="C27">
-        <v>0.1955872494896881</v>
+        <v>0.1954580125518941</v>
       </c>
       <c r="D27">
-        <v>0.1358013963981387</v>
+        <v>0.1373197523201167</v>
       </c>
       <c r="E27">
-        <v>0.171593805873011</v>
+        <v>0.171595041647547</v>
       </c>
       <c r="F27">
-        <v>0.01232083861344904</v>
+        <v>0.01231269745160126</v>
       </c>
       <c r="G27">
         <v>0.12</v>
       </c>
       <c r="H27">
-        <v>0.9024776112804669</v>
+        <v>0.9623676252084058</v>
       </c>
       <c r="I27">
         <v>0.1124550179928029</v>
       </c>
       <c r="J27">
-        <v>0.1124550179935385</v>
+        <v>0.112455017993504</v>
       </c>
       <c r="K27">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L27" t="s">
         <v>50</v>
       </c>
       <c r="M27">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="P27" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="Q27" t="s">
         <v>166</v>
       </c>
       <c r="R27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S27" t="s">
         <v>200</v>
@@ -2719,55 +2722,55 @@
         <v>44</v>
       </c>
       <c r="B28">
-        <v>0.1353905753571844</v>
+        <v>0.1282260148058714</v>
       </c>
       <c r="C28">
-        <v>0.1443641666246845</v>
+        <v>0.1442774328087733</v>
       </c>
       <c r="D28">
-        <v>0.1349923739025939</v>
+        <v>0.1337337072847106</v>
       </c>
       <c r="E28">
-        <v>0.1722564578836704</v>
+        <v>0.1722147369141076</v>
       </c>
       <c r="F28">
-        <v>0.009094087693285858</v>
+        <v>0.0090886239764487</v>
       </c>
       <c r="G28">
         <v>0.12</v>
       </c>
       <c r="H28">
-        <v>0.8863246181162805</v>
+        <v>0.9358475359440496</v>
       </c>
       <c r="I28">
         <v>0.09996001599360257</v>
       </c>
       <c r="J28">
-        <v>0.09996001599425644</v>
+        <v>0.09996001599422578</v>
       </c>
       <c r="K28">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L28" t="s">
         <v>50</v>
       </c>
       <c r="M28">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q28" t="s">
         <v>167</v>
       </c>
       <c r="R28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S28" t="s">
         <v>200</v>
@@ -2778,55 +2781,55 @@
         <v>45</v>
       </c>
       <c r="B29">
-        <v>0.1375227041688989</v>
+        <v>0.1373249102743785</v>
       </c>
       <c r="C29">
-        <v>0.1956749122746564</v>
+        <v>0.1955329061894823</v>
       </c>
       <c r="D29">
-        <v>0.09628462223567373</v>
+        <v>0.09471487952081561</v>
       </c>
       <c r="E29">
-        <v>0.1885566532792702</v>
+        <v>0.1884552852954027</v>
       </c>
       <c r="F29">
-        <v>0.01232636084983621</v>
+        <v>0.01231741530731172</v>
       </c>
       <c r="G29">
         <v>0.12</v>
       </c>
       <c r="H29">
-        <v>0.8725831907189789</v>
+        <v>0.873840002955306</v>
       </c>
       <c r="I29">
         <v>0.0899640143942423</v>
       </c>
       <c r="J29">
-        <v>0.08996401438879396</v>
+        <v>0.08996401438904929</v>
       </c>
       <c r="K29">
-        <v>0.9999999999394387</v>
+        <v>0.9999999999422767</v>
       </c>
       <c r="L29" t="s">
         <v>50</v>
       </c>
       <c r="M29">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q29" t="s">
         <v>168</v>
       </c>
       <c r="R29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="S29" t="s">
         <v>200</v>
@@ -2837,55 +2840,55 @@
         <v>46</v>
       </c>
       <c r="B30">
-        <v>0.1579950910574622</v>
+        <v>0.1556175660677405</v>
       </c>
       <c r="C30">
-        <v>0.1744067782752502</v>
+        <v>0.1744036900446199</v>
       </c>
       <c r="D30">
-        <v>0.197018940270914</v>
+        <v>0.203790975500498</v>
       </c>
       <c r="E30">
-        <v>0.1953891207600389</v>
+        <v>0.1956137069476523</v>
       </c>
       <c r="F30">
-        <v>0.01098659434000701</v>
+        <v>0.01098639979976323</v>
       </c>
       <c r="G30">
         <v>0.12</v>
       </c>
       <c r="H30">
-        <v>0.7595172685229598</v>
+        <v>0.7711211724501835</v>
       </c>
       <c r="I30">
         <v>0.04498200719712115</v>
       </c>
       <c r="J30">
-        <v>0.04498200719741539</v>
+        <v>0.04498200719740159</v>
       </c>
       <c r="K30">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L30" t="s">
         <v>50</v>
       </c>
       <c r="M30">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q30" t="s">
         <v>169</v>
       </c>
       <c r="R30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S30" t="s">
         <v>200</v>
@@ -2896,55 +2899,55 @@
         <v>47</v>
       </c>
       <c r="B31">
-        <v>0.1788562484976412</v>
+        <v>0.1777624223750275</v>
       </c>
       <c r="C31">
-        <v>0.2906748892047581</v>
+        <v>0.2905093239436632</v>
       </c>
       <c r="D31">
-        <v>0.1694679293871323</v>
+        <v>0.1728541198957731</v>
       </c>
       <c r="E31">
-        <v>0.2047411166752387</v>
+        <v>0.2049949555736964</v>
       </c>
       <c r="F31">
-        <v>0.01831079688588199</v>
+        <v>0.01830036725477225</v>
       </c>
       <c r="G31">
         <v>0.12</v>
       </c>
       <c r="H31">
-        <v>0.6709298724980389</v>
+        <v>0.6750583075810845</v>
       </c>
       <c r="I31">
         <v>0.03378648540583766</v>
       </c>
       <c r="J31">
-        <v>0.03378648540605866</v>
+        <v>0.0337864854060483</v>
       </c>
       <c r="K31">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L31" t="s">
         <v>50</v>
       </c>
       <c r="M31">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q31" t="s">
         <v>170</v>
       </c>
       <c r="R31" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="S31" t="s">
         <v>200</v>
@@ -2955,55 +2958,55 @@
         <v>48</v>
       </c>
       <c r="B32">
-        <v>0.1912158513513316</v>
+        <v>0.189993640881627</v>
       </c>
       <c r="C32">
-        <v>0.3119267354934455</v>
+        <v>0.3117674773473902</v>
       </c>
       <c r="D32">
-        <v>0.1916513898326096</v>
+        <v>0.1989134843737963</v>
       </c>
       <c r="E32">
-        <v>0.2409587885187901</v>
+        <v>0.2409867847174416</v>
       </c>
       <c r="F32">
-        <v>0.01964953736637812</v>
+        <v>0.01963950504617042</v>
       </c>
       <c r="G32">
         <v>0.12</v>
       </c>
       <c r="H32">
-        <v>0.6275630349259971</v>
+        <v>0.6316000864195471</v>
       </c>
       <c r="I32">
         <v>0.01129548180727709</v>
       </c>
       <c r="J32">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="K32">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L32" t="s">
         <v>50</v>
       </c>
       <c r="M32">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q32" t="s">
         <v>171</v>
       </c>
       <c r="R32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="S32" t="s">
         <v>200</v>
@@ -3014,55 +3017,55 @@
         <v>49</v>
       </c>
       <c r="B33">
-        <v>0.2100483874393241</v>
+        <v>0.2144832259760696</v>
       </c>
       <c r="C33">
-        <v>0.2867517797975319</v>
+        <v>0.2866675517735738</v>
       </c>
       <c r="D33">
-        <v>0.2288611038140106</v>
+        <v>0.2344223700902283</v>
       </c>
       <c r="E33">
-        <v>0.2857325296816159</v>
+        <v>0.2859915458182898</v>
       </c>
       <c r="F33">
-        <v>0.01806366422260535</v>
+        <v>0.01805835835582403</v>
       </c>
       <c r="G33">
         <v>0.12</v>
       </c>
       <c r="H33">
-        <v>0.5712969352581387</v>
+        <v>0.5594843114369636</v>
       </c>
       <c r="I33">
         <v>0.01129548180727709</v>
       </c>
       <c r="J33">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="K33">
-        <v>1.000000000006541</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L33" t="s">
         <v>50</v>
       </c>
       <c r="M33">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="N33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q33" t="s">
         <v>172</v>
       </c>
       <c r="R33" t="s">
-        <v>199</v>
+        <v>52</v>
       </c>
       <c r="S33" t="s">
         <v>200</v>
@@ -3116,22 +3119,22 @@
         <v>0.06747301079568173</v>
       </c>
       <c r="C2">
-        <v>0.1105449880348053</v>
+        <v>0.110051083502396</v>
       </c>
       <c r="D2">
         <v>0.12</v>
       </c>
       <c r="E2">
-        <v>1.085530896816578</v>
+        <v>1.090402712821882</v>
       </c>
       <c r="F2">
-        <v>0.07324403791995102</v>
+        <v>0.07357275401387146</v>
       </c>
       <c r="G2">
-        <v>0.06747301079610854</v>
+        <v>0.0674730107960885</v>
       </c>
       <c r="H2">
-        <v>0.005771027123842476</v>
+        <v>0.006099743217782963</v>
       </c>
       <c r="I2" t="s">
         <v>208</v>
@@ -3145,22 +3148,22 @@
         <v>0.08506597361055578</v>
       </c>
       <c r="C3">
-        <v>0.08693937630280837</v>
+        <v>0.08599260288294111</v>
       </c>
       <c r="D3">
         <v>0.12</v>
       </c>
       <c r="E3">
-        <v>1.380272151735274</v>
+        <v>1.395468865657573</v>
       </c>
       <c r="F3">
-        <v>0.1174141944348978</v>
+        <v>0.1187069177003793</v>
       </c>
       <c r="G3">
-        <v>0.08506597361111221</v>
+        <v>0.08506597361108613</v>
       </c>
       <c r="H3">
-        <v>0.03234822082378563</v>
+        <v>0.0336409440892932</v>
       </c>
       <c r="I3" t="s">
         <v>209</v>
@@ -3174,22 +3177,22 @@
         <v>0.005497800879648141</v>
       </c>
       <c r="C4">
-        <v>0.03988905080476223</v>
+        <v>0.03914619504344222</v>
       </c>
       <c r="D4">
         <v>0.12</v>
       </c>
       <c r="E4">
-        <v>3.008344334572974</v>
+        <v>3.065432026454444</v>
       </c>
       <c r="F4">
-        <v>0.0165392781288998</v>
+        <v>0.01685313489154282</v>
       </c>
       <c r="G4">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="H4">
-        <v>0.01104147724921569</v>
+        <v>0.01135533401186041</v>
       </c>
       <c r="I4" t="s">
         <v>210</v>
@@ -3203,22 +3206,22 @@
         <v>0.0505797680927629</v>
       </c>
       <c r="C5">
-        <v>0.05052690389806113</v>
+        <v>0.05181018488653797</v>
       </c>
       <c r="D5">
         <v>0.12</v>
       </c>
       <c r="E5">
-        <v>2.374972356155089</v>
+        <v>2.316146917112817</v>
       </c>
       <c r="F5">
-        <v>0.1201255510010471</v>
+        <v>0.117150173936334</v>
       </c>
       <c r="G5">
-        <v>0.05057976809309375</v>
+        <v>0.05057976809307824</v>
       </c>
       <c r="H5">
-        <v>0.06954578290795334</v>
+        <v>0.06657040584325577</v>
       </c>
       <c r="I5" t="s">
         <v>211</v>
@@ -3232,22 +3235,22 @@
         <v>0.01859256297481008</v>
       </c>
       <c r="C6">
-        <v>0.0473013380209173</v>
+        <v>0.04770117265223589</v>
       </c>
       <c r="D6">
         <v>0.12</v>
       </c>
       <c r="E6">
-        <v>2.536926121348499</v>
+        <v>2.515661425660471</v>
       </c>
       <c r="F6">
-        <v>0.04716795867361263</v>
+        <v>0.04677259347989279</v>
       </c>
       <c r="G6">
-        <v>0.01859256297493169</v>
+        <v>0.01859256297492599</v>
       </c>
       <c r="H6">
-        <v>0.02857539569868093</v>
+        <v>0.0281800305049668</v>
       </c>
       <c r="I6" t="s">
         <v>212</v>
@@ -3261,22 +3264,22 @@
         <v>0.01859256297481008</v>
       </c>
       <c r="C7">
-        <v>0.06562669675920818</v>
+        <v>0.06469555905163277</v>
       </c>
       <c r="D7">
         <v>0.12</v>
       </c>
       <c r="E7">
-        <v>1.828524151387562</v>
+        <v>1.85484137951771</v>
       </c>
       <c r="F7">
-        <v>0.03399695043563439</v>
+        <v>0.03448625515696662</v>
       </c>
       <c r="G7">
-        <v>0.01859256297493169</v>
+        <v>0.01859256297492599</v>
       </c>
       <c r="H7">
-        <v>0.0154043874607027</v>
+        <v>0.01589369218204063</v>
       </c>
       <c r="I7" t="s">
         <v>213</v>
@@ -3290,22 +3293,22 @@
         <v>0.01129548180727709</v>
       </c>
       <c r="C8">
-        <v>0.2100483874393241</v>
+        <v>0.2144832259760696</v>
       </c>
       <c r="D8">
         <v>0.12</v>
       </c>
       <c r="E8">
-        <v>0.5712969352581387</v>
+        <v>0.5594843114369636</v>
       </c>
       <c r="F8">
-        <v>0.006453074138761463</v>
+        <v>0.006319644861293171</v>
       </c>
       <c r="G8">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="H8">
-        <v>0.004842407668589511</v>
+        <v>0.00497583694605434</v>
       </c>
       <c r="I8" t="s">
         <v>214</v>
@@ -3319,22 +3322,22 @@
         <v>0.01129548180727709</v>
       </c>
       <c r="C9">
-        <v>0.1912158513513316</v>
+        <v>0.189993640881627</v>
       </c>
       <c r="D9">
         <v>0.12</v>
       </c>
       <c r="E9">
-        <v>0.6275630349259971</v>
+        <v>0.6316000864195471</v>
       </c>
       <c r="F9">
-        <v>0.007088626843926196</v>
+        <v>0.007134227285626632</v>
       </c>
       <c r="G9">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="H9">
-        <v>0.004206854963424778</v>
+        <v>0.00416125452172088</v>
       </c>
       <c r="I9" t="s">
         <v>215</v>
@@ -3348,22 +3351,22 @@
         <v>0.02249100359856058</v>
       </c>
       <c r="C10">
-        <v>0.1147106489165815</v>
+        <v>0.1120818178495579</v>
       </c>
       <c r="D10">
         <v>0.12</v>
       </c>
       <c r="E10">
-        <v>1.046110375395618</v>
+        <v>1.070646446518831</v>
       </c>
       <c r="F10">
-        <v>0.0235280722175144</v>
+        <v>0.02407991308144112</v>
       </c>
       <c r="G10">
-        <v>0.02249100359870769</v>
+        <v>0.0224910035987008</v>
       </c>
       <c r="H10">
-        <v>0.001037068618806709</v>
+        <v>0.001588909482740323</v>
       </c>
       <c r="I10" t="s">
         <v>216</v>
@@ -3377,22 +3380,22 @@
         <v>0.04498200719712115</v>
       </c>
       <c r="C11">
-        <v>0.1579950910574622</v>
+        <v>0.1556175660677405</v>
       </c>
       <c r="D11">
         <v>0.12</v>
       </c>
       <c r="E11">
-        <v>0.7595172685229598</v>
+        <v>0.7711211724501835</v>
       </c>
       <c r="F11">
-        <v>0.03416461123903757</v>
+        <v>0.03468657812900666</v>
       </c>
       <c r="G11">
-        <v>0.04498200719741539</v>
+        <v>0.04498200719740159</v>
       </c>
       <c r="H11">
-        <v>0.01081739595837782</v>
+        <v>0.01029542906839494</v>
       </c>
       <c r="I11" t="s">
         <v>217</v>
@@ -3406,22 +3409,22 @@
         <v>0.007297081167532987</v>
       </c>
       <c r="C12">
-        <v>0.06053476212570217</v>
+        <v>0.06067006888567235</v>
       </c>
       <c r="D12">
         <v>0.12</v>
       </c>
       <c r="E12">
-        <v>1.982332064852531</v>
+        <v>1.977911055715627</v>
       </c>
       <c r="F12">
-        <v>0.01446523797823219</v>
+        <v>0.01443297751571779</v>
       </c>
       <c r="G12">
-        <v>0.007297081167091044</v>
+        <v>0.007297081167111755</v>
       </c>
       <c r="H12">
-        <v>0.007168156811141143</v>
+        <v>0.007135896348606034</v>
       </c>
       <c r="I12" t="s">
         <v>218</v>
@@ -3435,22 +3438,22 @@
         <v>0.005497800879648141</v>
       </c>
       <c r="C13">
-        <v>0.03563311718442798</v>
+        <v>0.03694532067208307</v>
       </c>
       <c r="D13">
         <v>0.12</v>
       </c>
       <c r="E13">
-        <v>3.367653730065501</v>
+        <v>3.248043265481125</v>
       </c>
       <c r="F13">
-        <v>0.01851468963950445</v>
+        <v>0.01785709512209735</v>
       </c>
       <c r="G13">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="H13">
-        <v>0.01301688875982035</v>
+        <v>0.01235929424241493</v>
       </c>
       <c r="I13" t="s">
         <v>219</v>
@@ -3464,22 +3467,22 @@
         <v>0.09996001599360257</v>
       </c>
       <c r="C14">
-        <v>0.1353905753571844</v>
+        <v>0.1282260148058714</v>
       </c>
       <c r="D14">
         <v>0.12</v>
       </c>
       <c r="E14">
-        <v>0.8863246181162805</v>
+        <v>0.9358475359440496</v>
       </c>
       <c r="F14">
-        <v>0.0885970230024271</v>
+        <v>0.09354733466054076</v>
       </c>
       <c r="G14">
-        <v>0.09996001599425644</v>
+        <v>0.09996001599422578</v>
       </c>
       <c r="H14">
-        <v>0.01136299299182934</v>
+        <v>0.006412681333685027</v>
       </c>
       <c r="I14" t="s">
         <v>220</v>
@@ -3493,22 +3496,22 @@
         <v>0.005497800879648141</v>
       </c>
       <c r="C15">
-        <v>0.0856051699082177</v>
+        <v>0.08358202127746187</v>
       </c>
       <c r="D15">
         <v>0.12</v>
       </c>
       <c r="E15">
-        <v>1.401784496528177</v>
+        <v>1.435715458491291</v>
       </c>
       <c r="F15">
-        <v>0.007706732038089737</v>
+        <v>0.007893277710617853</v>
       </c>
       <c r="G15">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="H15">
-        <v>0.002208931158405634</v>
+        <v>0.002395476830935436</v>
       </c>
       <c r="I15" t="s">
         <v>221</v>
@@ -3516,28 +3519,28 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>0.04498200719712115</v>
       </c>
       <c r="C16">
-        <v>0.1163107796790405</v>
+        <v>0.1217349660257986</v>
       </c>
       <c r="D16">
         <v>0.12</v>
       </c>
       <c r="E16">
-        <v>1.031718644919585</v>
+        <v>0.985748005832351</v>
       </c>
       <c r="F16">
-        <v>0.04640877551117684</v>
+        <v>0.04434092389289863</v>
       </c>
       <c r="G16">
-        <v>0.04498200719741539</v>
+        <v>0.04498200719740159</v>
       </c>
       <c r="H16">
-        <v>0.001426768313761456</v>
+        <v>0.0006410833045029582</v>
       </c>
       <c r="I16" t="s">
         <v>222</v>
@@ -3551,22 +3554,22 @@
         <v>0.06377449020391843</v>
       </c>
       <c r="C17">
-        <v>0.05905167052056143</v>
+        <v>0.05563680009278063</v>
       </c>
       <c r="D17">
         <v>0.12</v>
       </c>
       <c r="E17">
-        <v>2.032118633429967</v>
+        <v>2.156845825063384</v>
       </c>
       <c r="F17">
-        <v>0.1295973298808795</v>
+        <v>0.1375517429418671</v>
       </c>
       <c r="G17">
-        <v>0.06377449020433559</v>
+        <v>0.06377449020431604</v>
       </c>
       <c r="H17">
-        <v>0.06582283967654395</v>
+        <v>0.07377725273755111</v>
       </c>
       <c r="I17" t="s">
         <v>223</v>
@@ -3580,22 +3583,22 @@
         <v>0.03378648540583766</v>
       </c>
       <c r="C18">
-        <v>0.1788562484976412</v>
+        <v>0.1777624223750275</v>
       </c>
       <c r="D18">
         <v>0.12</v>
       </c>
       <c r="E18">
-        <v>0.6709298724980389</v>
+        <v>0.6750583075810845</v>
       </c>
       <c r="F18">
-        <v>0.02266836234549552</v>
+        <v>0.02280784765717778</v>
       </c>
       <c r="G18">
-        <v>0.03378648540605866</v>
+        <v>0.0337864854060483</v>
       </c>
       <c r="H18">
-        <v>0.01111812306056315</v>
+        <v>0.01097863774887052</v>
       </c>
       <c r="I18" t="s">
         <v>224</v>
@@ -3609,22 +3612,22 @@
         <v>0.0899640143942423</v>
       </c>
       <c r="C19">
-        <v>0.1375227041688989</v>
+        <v>0.1373249102743785</v>
       </c>
       <c r="D19">
         <v>0.12</v>
       </c>
       <c r="E19">
-        <v>0.8725831907189789</v>
+        <v>0.873840002955306</v>
       </c>
       <c r="F19">
-        <v>0.0785010867300161</v>
+        <v>0.07861415460413589</v>
       </c>
       <c r="G19">
-        <v>0.08996401438879396</v>
+        <v>0.08996401438904929</v>
       </c>
       <c r="H19">
-        <v>0.01146292765877786</v>
+        <v>0.0113498597849134</v>
       </c>
       <c r="I19" t="s">
         <v>225</v>
@@ -3638,22 +3641,22 @@
         <v>0.01129548180727709</v>
       </c>
       <c r="C20">
-        <v>0.1286455579513547</v>
+        <v>0.1221898841733612</v>
       </c>
       <c r="D20">
         <v>0.12</v>
       </c>
       <c r="E20">
-        <v>0.9327955190289281</v>
+        <v>0.9820780239855681</v>
       </c>
       <c r="F20">
-        <v>0.01053637481510085</v>
+        <v>0.01109304445325562</v>
       </c>
       <c r="G20">
-        <v>0.01129548180735097</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="H20">
-        <v>0.0007591069922501265</v>
+        <v>0.0002024373540918945</v>
       </c>
       <c r="I20" t="s">
         <v>226</v>
@@ -3667,22 +3670,22 @@
         <v>0.06377449020391843</v>
       </c>
       <c r="C21">
-        <v>0.07818290359200544</v>
+        <v>0.07745530214105066</v>
       </c>
       <c r="D21">
         <v>0.12</v>
       </c>
       <c r="E21">
-        <v>1.534862412199673</v>
+        <v>1.54928063906423</v>
       </c>
       <c r="F21">
-        <v>0.09788506787119068</v>
+        <v>0.09880458293912221</v>
       </c>
       <c r="G21">
-        <v>0.06377449020433559</v>
+        <v>0.06377449020431604</v>
       </c>
       <c r="H21">
-        <v>0.03411057766685509</v>
+        <v>0.03503009273480617</v>
       </c>
       <c r="I21" t="s">
         <v>227</v>
@@ -3696,22 +3699,22 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C22">
-        <v>0.01763245787306867</v>
+        <v>0.01762469926214086</v>
       </c>
       <c r="D22">
         <v>0.12</v>
       </c>
       <c r="E22">
-        <v>6.805630891838662</v>
+        <v>6.808626814856849</v>
       </c>
       <c r="F22">
-        <v>0.06190647852432211</v>
+        <v>0.06193373052298814</v>
       </c>
       <c r="G22">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H22">
-        <v>0.05281011706884477</v>
+        <v>0.05283736906751359</v>
       </c>
       <c r="I22" t="s">
         <v>228</v>
@@ -3725,22 +3728,22 @@
         <v>0.01009596161535386</v>
       </c>
       <c r="C23">
-        <v>0.04435880841436476</v>
+        <v>0.04523816926953131</v>
       </c>
       <c r="D23">
         <v>0.12</v>
       </c>
       <c r="E23">
-        <v>2.705212432197351</v>
+        <v>2.652627237964337</v>
       </c>
       <c r="F23">
-        <v>0.02731172087684251</v>
+        <v>0.02678082277433008</v>
       </c>
       <c r="G23">
-        <v>0.0100959616154199</v>
+        <v>0.0100959616154168</v>
       </c>
       <c r="H23">
-        <v>0.01721575926142261</v>
+        <v>0.01668486115891327</v>
       </c>
       <c r="I23" t="s">
         <v>229</v>
@@ -3754,22 +3757,22 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C24">
-        <v>0.04249235515673782</v>
+        <v>0.0425423662168037</v>
       </c>
       <c r="D24">
         <v>0.12</v>
       </c>
       <c r="E24">
-        <v>2.824037395841358</v>
+        <v>2.820717573358708</v>
       </c>
       <c r="F24">
-        <v>0.02568846491618989</v>
+        <v>0.02565826661091988</v>
       </c>
       <c r="G24">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H24">
-        <v>0.01659210346071256</v>
+        <v>0.01656190515544533</v>
       </c>
       <c r="I24" t="s">
         <v>230</v>
@@ -3783,22 +3786,22 @@
         <v>0.005497800879648141</v>
       </c>
       <c r="C25">
-        <v>0.03490342407671233</v>
+        <v>0.03502611942537402</v>
       </c>
       <c r="D25">
         <v>0.12</v>
       </c>
       <c r="E25">
-        <v>3.438058103877103</v>
+        <v>3.426014698992554</v>
       </c>
       <c r="F25">
-        <v>0.01890175886777695</v>
+        <v>0.01883554662580872</v>
       </c>
       <c r="G25">
-        <v>0.005497800879684103</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="H25">
-        <v>0.01340395798809285</v>
+        <v>0.0133377457461263</v>
       </c>
       <c r="I25" t="s">
         <v>231</v>
@@ -3812,22 +3815,22 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C26">
-        <v>0.01791338682827996</v>
+        <v>0.01809404311665208</v>
       </c>
       <c r="D26">
         <v>0.12</v>
       </c>
       <c r="E26">
-        <v>6.69890072437644</v>
+        <v>6.632016914426557</v>
       </c>
       <c r="F26">
-        <v>0.06093562234288846</v>
+        <v>0.06032722303206885</v>
       </c>
       <c r="G26">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H26">
-        <v>0.05183926088741112</v>
+        <v>0.0512308615765943</v>
       </c>
       <c r="I26" t="s">
         <v>232</v>
@@ -3835,31 +3838,31 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>0.009096361455417834</v>
       </c>
       <c r="C27">
-        <v>0.1179763332508383</v>
+        <v>0.1215164053503871</v>
       </c>
       <c r="D27">
         <v>0.12</v>
       </c>
       <c r="E27">
-        <v>1.017153158547986</v>
+        <v>0.9875209824877997</v>
       </c>
       <c r="F27">
-        <v>0.009252392785672409</v>
+        <v>0.008982847801518371</v>
       </c>
       <c r="G27">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H27">
-        <v>0.0001560313301950736</v>
+        <v>0.0001135136539561748</v>
       </c>
       <c r="I27" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3870,25 +3873,25 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C28">
-        <v>0.04548321420369619</v>
+        <v>0.04551625614122628</v>
       </c>
       <c r="D28">
         <v>0.12</v>
       </c>
       <c r="E28">
-        <v>2.638335968574714</v>
+        <v>2.636420702697254</v>
       </c>
       <c r="F28">
-        <v>0.02399925761098551</v>
+        <v>0.02398183566028091</v>
       </c>
       <c r="G28">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H28">
-        <v>0.01490289615550817</v>
+        <v>0.01488547420480636</v>
       </c>
       <c r="I28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3899,25 +3902,25 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C29">
-        <v>0.08847231604195015</v>
+        <v>0.0893857405791231</v>
       </c>
       <c r="D29">
         <v>0.12</v>
       </c>
       <c r="E29">
-        <v>1.356356489448074</v>
+        <v>1.342496009123262</v>
       </c>
       <c r="F29">
-        <v>0.0123379088904213</v>
+        <v>0.01221182895144111</v>
       </c>
       <c r="G29">
-        <v>0.009096361455477335</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="H29">
-        <v>0.003241547434943969</v>
+        <v>0.003115467495966567</v>
       </c>
       <c r="I29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3928,80 +3931,80 @@
         <v>0.1124550179928029</v>
       </c>
       <c r="C30">
-        <v>0.132967287498401</v>
+        <v>0.1246924739119454</v>
       </c>
       <c r="D30">
         <v>0.12</v>
       </c>
       <c r="E30">
-        <v>0.9024776112804669</v>
+        <v>0.9623676252084058</v>
       </c>
       <c r="F30">
-        <v>0.1014881360146467</v>
+        <v>0.1082230686085023</v>
       </c>
       <c r="G30">
-        <v>0.1124550179935385</v>
+        <v>0.112455017993504</v>
       </c>
       <c r="H30">
-        <v>0.01096688197889181</v>
+        <v>0.004231949385001738</v>
       </c>
       <c r="I30" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>0.007297081167532987</v>
       </c>
       <c r="C31">
-        <v>0.04803882356860375</v>
+        <v>0.04853638764815744</v>
       </c>
       <c r="D31">
         <v>0.12</v>
       </c>
       <c r="E31">
-        <v>2.497979573305521</v>
+        <v>2.472371880451542</v>
       </c>
       <c r="F31">
-        <v>0.0182279597012498</v>
+        <v>0.01804109828798106</v>
       </c>
       <c r="G31">
-        <v>0.007297081167580719</v>
+        <v>0.007297081167578481</v>
       </c>
       <c r="H31">
-        <v>0.01093087853366908</v>
+        <v>0.01074401712040258</v>
       </c>
       <c r="I31" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>0.02479008396641344</v>
       </c>
       <c r="C32">
-        <v>0.04796765594392619</v>
+        <v>0.04935812195542288</v>
       </c>
       <c r="D32">
         <v>0.12</v>
       </c>
       <c r="E32">
-        <v>2.50168572215159</v>
+        <v>2.431210816902158</v>
       </c>
       <c r="F32">
-        <v>0.06201699910971556</v>
+        <v>0.06026992029105709</v>
       </c>
       <c r="G32">
-        <v>0.02479008396657559</v>
+        <v>0.02479008396656799</v>
       </c>
       <c r="H32">
-        <v>0.03722691514313996</v>
+        <v>0.03547983632448909</v>
       </c>
       <c r="I32" t="s">
         <v>237</v>
@@ -4015,25 +4018,25 @@
         <v>0.0235905637744902</v>
       </c>
       <c r="C33">
-        <v>0.08793597123031011</v>
+        <v>0.08795103108520301</v>
       </c>
       <c r="D33">
         <v>0.12</v>
       </c>
       <c r="E33">
-        <v>1.364629267421316</v>
+        <v>1.364395601954335</v>
       </c>
       <c r="F33">
-        <v>0.03219237376163839</v>
+        <v>0.03218686146153769</v>
       </c>
       <c r="G33">
-        <v>0.02359056377464451</v>
+        <v>0.02359056377463728</v>
       </c>
       <c r="H33">
-        <v>0.008601809986993881</v>
+        <v>0.008596297686900414</v>
       </c>
       <c r="I33" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4052,52 +4055,52 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B2">
-        <v>0.08802105798928705</v>
+        <v>0.08745570542123857</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B3">
-        <v>0.08189403675011157</v>
+        <v>0.08051866170925626</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B4">
-        <v>0.01763245787306867</v>
+        <v>0.01762469926214086</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B5">
-        <v>0.2100483874393241</v>
+        <v>0.2144832259760696</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B6">
-        <v>0.05061414951847965</v>
+        <v>0.05022194633741913</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -4105,7 +4108,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -4121,18 +4124,18 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B10">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/perplexity_examples/instrument_volatility_analysis.xlsx
+++ b/perplexity_examples/instrument_volatility_analysis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="218">
   <si>
     <t>System_Used_Vol_Annual</t>
   </si>
@@ -72,10 +72,22 @@
     <t>Target_Vol_Formatted</t>
   </si>
   <si>
+    <t>SPSB</t>
+  </si>
+  <si>
     <t>SCHO</t>
   </si>
   <si>
-    <t>SPSB</t>
+    <t>SCHR</t>
+  </si>
+  <si>
+    <t>SCHP</t>
+  </si>
+  <si>
+    <t>CMBS</t>
+  </si>
+  <si>
+    <t>VCIT</t>
   </si>
   <si>
     <t>SPHY</t>
@@ -84,75 +96,63 @@
     <t>HYLB</t>
   </si>
   <si>
-    <t>CMBS</t>
-  </si>
-  <si>
-    <t>SCHR</t>
-  </si>
-  <si>
-    <t>SCHP</t>
-  </si>
-  <si>
-    <t>VCIT</t>
+    <t>VMBS</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>IHY</t>
+  </si>
+  <si>
+    <t>VWOB</t>
+  </si>
+  <si>
+    <t>EMB</t>
   </si>
   <si>
     <t>EMHY</t>
   </si>
   <si>
-    <t>VMBS</t>
-  </si>
-  <si>
-    <t>VWOB</t>
-  </si>
-  <si>
-    <t>EMB</t>
-  </si>
-  <si>
-    <t>IHY</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
     <t>EMLC</t>
   </si>
   <si>
     <t>PICB</t>
   </si>
   <si>
+    <t>BWX</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
     <t>ICVT</t>
   </si>
   <si>
-    <t>BWX</t>
-  </si>
-  <si>
-    <t>WIP</t>
-  </si>
-  <si>
     <t>VCLT</t>
   </si>
   <si>
+    <t>SPTL</t>
+  </si>
+  <si>
+    <t>KSA</t>
+  </si>
+  <si>
+    <t>FLCA</t>
+  </si>
+  <si>
+    <t>VGK</t>
+  </si>
+  <si>
+    <t>IAU</t>
+  </si>
+  <si>
+    <t>IEMG</t>
+  </si>
+  <si>
     <t>BBAX</t>
   </si>
   <si>
-    <t>FLCA</t>
-  </si>
-  <si>
-    <t>SPTL</t>
-  </si>
-  <si>
-    <t>IEMG</t>
-  </si>
-  <si>
-    <t>KSA</t>
-  </si>
-  <si>
-    <t>VGK</t>
-  </si>
-  <si>
-    <t>IAU</t>
-  </si>
-  <si>
     <t>IVV</t>
   </si>
   <si>
@@ -171,453 +171,366 @@
     <t>Manual_Calculation</t>
   </si>
   <si>
-    <t>1.76%</t>
+    <t>1.58%</t>
+  </si>
+  <si>
+    <t>1.68%</t>
+  </si>
+  <si>
+    <t>4.33%</t>
+  </si>
+  <si>
+    <t>4.60%</t>
+  </si>
+  <si>
+    <t>5.28%</t>
+  </si>
+  <si>
+    <t>5.45%</t>
+  </si>
+  <si>
+    <t>5.50%</t>
+  </si>
+  <si>
+    <t>5.52%</t>
+  </si>
+  <si>
+    <t>6.33%</t>
+  </si>
+  <si>
+    <t>6.35%</t>
+  </si>
+  <si>
+    <t>6.59%</t>
+  </si>
+  <si>
+    <t>7.06%</t>
+  </si>
+  <si>
+    <t>7.09%</t>
+  </si>
+  <si>
+    <t>7.29%</t>
+  </si>
+  <si>
+    <t>8.38%</t>
+  </si>
+  <si>
+    <t>8.98%</t>
+  </si>
+  <si>
+    <t>9.98%</t>
+  </si>
+  <si>
+    <t>10.37%</t>
+  </si>
+  <si>
+    <t>11.10%</t>
+  </si>
+  <si>
+    <t>11.99%</t>
+  </si>
+  <si>
+    <t>13.97%</t>
+  </si>
+  <si>
+    <t>15.74%</t>
+  </si>
+  <si>
+    <t>17.16%</t>
+  </si>
+  <si>
+    <t>17.22%</t>
+  </si>
+  <si>
+    <t>17.96%</t>
+  </si>
+  <si>
+    <t>18.66%</t>
+  </si>
+  <si>
+    <t>18.85%</t>
+  </si>
+  <si>
+    <t>19.56%</t>
+  </si>
+  <si>
+    <t>20.50%</t>
+  </si>
+  <si>
+    <t>24.10%</t>
+  </si>
+  <si>
+    <t>28.60%</t>
+  </si>
+  <si>
+    <t>3.38%</t>
+  </si>
+  <si>
+    <t>1.66%</t>
+  </si>
+  <si>
+    <t>4.73%</t>
+  </si>
+  <si>
+    <t>5.97%</t>
+  </si>
+  <si>
+    <t>6.13%</t>
+  </si>
+  <si>
+    <t>6.75%</t>
+  </si>
+  <si>
+    <t>8.18%</t>
+  </si>
+  <si>
+    <t>8.78%</t>
+  </si>
+  <si>
+    <t>5.82%</t>
+  </si>
+  <si>
+    <t>14.44%</t>
+  </si>
+  <si>
+    <t>10.08%</t>
+  </si>
+  <si>
+    <t>10.70%</t>
+  </si>
+  <si>
+    <t>11.58%</t>
+  </si>
+  <si>
+    <t>10.10%</t>
+  </si>
+  <si>
+    <t>10.33%</t>
+  </si>
+  <si>
+    <t>8.88%</t>
+  </si>
+  <si>
+    <t>10.53%</t>
+  </si>
+  <si>
+    <t>16.26%</t>
+  </si>
+  <si>
+    <t>13.80%</t>
+  </si>
+  <si>
+    <t>14.69%</t>
+  </si>
+  <si>
+    <t>20.48%</t>
+  </si>
+  <si>
+    <t>19.24%</t>
+  </si>
+  <si>
+    <t>19.55%</t>
+  </si>
+  <si>
+    <t>14.43%</t>
+  </si>
+  <si>
+    <t>20.40%</t>
+  </si>
+  <si>
+    <t>19.77%</t>
+  </si>
+  <si>
+    <t>17.44%</t>
+  </si>
+  <si>
+    <t>29.05%</t>
+  </si>
+  <si>
+    <t>31.18%</t>
+  </si>
+  <si>
+    <t>28.67%</t>
+  </si>
+  <si>
+    <t>1.78%</t>
+  </si>
+  <si>
+    <t>1.83%</t>
+  </si>
+  <si>
+    <t>4.12%</t>
+  </si>
+  <si>
+    <t>3.91%</t>
+  </si>
+  <si>
+    <t>4.29%</t>
+  </si>
+  <si>
+    <t>2.68%</t>
+  </si>
+  <si>
+    <t>2.73%</t>
+  </si>
+  <si>
+    <t>4.64%</t>
+  </si>
+  <si>
+    <t>4.76%</t>
+  </si>
+  <si>
+    <t>5.61%</t>
+  </si>
+  <si>
+    <t>4.31%</t>
+  </si>
+  <si>
+    <t>4.50%</t>
+  </si>
+  <si>
+    <t>3.93%</t>
+  </si>
+  <si>
+    <t>5.90%</t>
+  </si>
+  <si>
+    <t>7.31%</t>
+  </si>
+  <si>
+    <t>8.56%</t>
+  </si>
+  <si>
+    <t>8.15%</t>
+  </si>
+  <si>
+    <t>7.22%</t>
+  </si>
+  <si>
+    <t>8.19%</t>
+  </si>
+  <si>
+    <t>10.49%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>10.99%</t>
+  </si>
+  <si>
+    <t>13.73%</t>
+  </si>
+  <si>
+    <t>13.37%</t>
+  </si>
+  <si>
+    <t>10.81%</t>
+  </si>
+  <si>
+    <t>10.71%</t>
+  </si>
+  <si>
+    <t>9.47%</t>
+  </si>
+  <si>
+    <t>20.38%</t>
+  </si>
+  <si>
+    <t>17.29%</t>
+  </si>
+  <si>
+    <t>19.89%</t>
+  </si>
+  <si>
+    <t>23.44%</t>
+  </si>
+  <si>
+    <t>0.21%</t>
+  </si>
+  <si>
+    <t>0.10%</t>
+  </si>
+  <si>
+    <t>0.30%</t>
+  </si>
+  <si>
+    <t>0.38%</t>
+  </si>
+  <si>
+    <t>0.39%</t>
+  </si>
+  <si>
+    <t>0.43%</t>
+  </si>
+  <si>
+    <t>0.51%</t>
+  </si>
+  <si>
+    <t>0.55%</t>
+  </si>
+  <si>
+    <t>0.37%</t>
+  </si>
+  <si>
+    <t>0.91%</t>
+  </si>
+  <si>
+    <t>0.52%</t>
+  </si>
+  <si>
+    <t>0.64%</t>
+  </si>
+  <si>
+    <t>0.67%</t>
+  </si>
+  <si>
+    <t>0.73%</t>
+  </si>
+  <si>
+    <t>0.65%</t>
+  </si>
+  <si>
+    <t>0.56%</t>
+  </si>
+  <si>
+    <t>0.66%</t>
+  </si>
+  <si>
+    <t>1.02%</t>
+  </si>
+  <si>
+    <t>0.87%</t>
+  </si>
+  <si>
+    <t>0.93%</t>
+  </si>
+  <si>
+    <t>1.29%</t>
+  </si>
+  <si>
+    <t>1.21%</t>
+  </si>
+  <si>
+    <t>1.23%</t>
+  </si>
+  <si>
+    <t>1.28%</t>
+  </si>
+  <si>
+    <t>1.25%</t>
+  </si>
+  <si>
+    <t>1.10%</t>
+  </si>
+  <si>
+    <t>1.96%</t>
   </si>
   <si>
     <t>1.81%</t>
   </si>
   <si>
-    <t>3.50%</t>
-  </si>
-  <si>
-    <t>3.69%</t>
-  </si>
-  <si>
-    <t>3.91%</t>
-  </si>
-  <si>
-    <t>4.25%</t>
-  </si>
-  <si>
-    <t>4.52%</t>
-  </si>
-  <si>
-    <t>4.55%</t>
-  </si>
-  <si>
-    <t>4.77%</t>
-  </si>
-  <si>
-    <t>4.85%</t>
-  </si>
-  <si>
-    <t>4.94%</t>
-  </si>
-  <si>
-    <t>5.18%</t>
-  </si>
-  <si>
-    <t>5.56%</t>
-  </si>
-  <si>
-    <t>6.07%</t>
-  </si>
-  <si>
-    <t>6.47%</t>
-  </si>
-  <si>
-    <t>7.75%</t>
-  </si>
-  <si>
-    <t>8.36%</t>
-  </si>
-  <si>
-    <t>8.60%</t>
-  </si>
-  <si>
-    <t>8.80%</t>
-  </si>
-  <si>
-    <t>8.94%</t>
-  </si>
-  <si>
-    <t>11.01%</t>
-  </si>
-  <si>
-    <t>11.21%</t>
-  </si>
-  <si>
-    <t>12.15%</t>
-  </si>
-  <si>
-    <t>12.17%</t>
-  </si>
-  <si>
-    <t>12.22%</t>
-  </si>
-  <si>
-    <t>12.47%</t>
-  </si>
-  <si>
-    <t>12.82%</t>
-  </si>
-  <si>
-    <t>13.73%</t>
-  </si>
-  <si>
-    <t>15.56%</t>
-  </si>
-  <si>
-    <t>17.78%</t>
-  </si>
-  <si>
-    <t>19.00%</t>
-  </si>
-  <si>
-    <t>21.45%</t>
-  </si>
-  <si>
-    <t>1.66%</t>
-  </si>
-  <si>
-    <t>3.38%</t>
-  </si>
-  <si>
-    <t>8.18%</t>
-  </si>
-  <si>
-    <t>8.78%</t>
-  </si>
-  <si>
-    <t>6.13%</t>
-  </si>
-  <si>
-    <t>4.73%</t>
-  </si>
-  <si>
-    <t>5.97%</t>
-  </si>
-  <si>
-    <t>6.75%</t>
-  </si>
-  <si>
-    <t>11.58%</t>
-  </si>
-  <si>
-    <t>5.82%</t>
-  </si>
-  <si>
-    <t>10.08%</t>
-  </si>
-  <si>
-    <t>10.70%</t>
-  </si>
-  <si>
-    <t>14.44%</t>
-  </si>
-  <si>
-    <t>10.10%</t>
-  </si>
-  <si>
-    <t>10.33%</t>
-  </si>
-  <si>
-    <t>16.26%</t>
-  </si>
-  <si>
-    <t>8.88%</t>
-  </si>
-  <si>
-    <t>10.53%</t>
-  </si>
-  <si>
-    <t>13.80%</t>
-  </si>
-  <si>
-    <t>19.77%</t>
-  </si>
-  <si>
-    <t>19.24%</t>
-  </si>
-  <si>
-    <t>14.69%</t>
-  </si>
-  <si>
-    <t>20.40%</t>
-  </si>
-  <si>
-    <t>20.48%</t>
-  </si>
-  <si>
-    <t>19.55%</t>
-  </si>
-  <si>
-    <t>14.43%</t>
-  </si>
-  <si>
-    <t>17.44%</t>
-  </si>
-  <si>
-    <t>29.05%</t>
-  </si>
-  <si>
-    <t>31.18%</t>
-  </si>
-  <si>
-    <t>28.67%</t>
-  </si>
-  <si>
-    <t>1.83%</t>
-  </si>
-  <si>
-    <t>1.78%</t>
-  </si>
-  <si>
-    <t>2.68%</t>
-  </si>
-  <si>
-    <t>2.73%</t>
-  </si>
-  <si>
-    <t>4.12%</t>
-  </si>
-  <si>
-    <t>4.29%</t>
-  </si>
-  <si>
-    <t>3.93%</t>
-  </si>
-  <si>
-    <t>4.64%</t>
-  </si>
-  <si>
-    <t>4.31%</t>
-  </si>
-  <si>
-    <t>4.50%</t>
-  </si>
-  <si>
-    <t>5.61%</t>
-  </si>
-  <si>
-    <t>4.76%</t>
-  </si>
-  <si>
-    <t>5.90%</t>
-  </si>
-  <si>
-    <t>7.31%</t>
-  </si>
-  <si>
-    <t>7.22%</t>
-  </si>
-  <si>
-    <t>8.56%</t>
-  </si>
-  <si>
-    <t>8.15%</t>
-  </si>
-  <si>
-    <t>8.19%</t>
-  </si>
-  <si>
-    <t>10.71%</t>
-  </si>
-  <si>
-    <t>10.99%</t>
-  </si>
-  <si>
-    <t>10.49%</t>
-  </si>
-  <si>
-    <t>10.81%</t>
-  </si>
-  <si>
-    <t>9.54%</t>
-  </si>
-  <si>
-    <t>13.37%</t>
-  </si>
-  <si>
-    <t>9.47%</t>
-  </si>
-  <si>
-    <t>20.38%</t>
-  </si>
-  <si>
-    <t>17.29%</t>
-  </si>
-  <si>
-    <t>19.89%</t>
-  </si>
-  <si>
-    <t>23.44%</t>
-  </si>
-  <si>
-    <t>1.68%</t>
-  </si>
-  <si>
-    <t>1.58%</t>
-  </si>
-  <si>
-    <t>5.45%</t>
-  </si>
-  <si>
-    <t>5.50%</t>
-  </si>
-  <si>
-    <t>4.60%</t>
-  </si>
-  <si>
-    <t>4.33%</t>
-  </si>
-  <si>
-    <t>5.28%</t>
-  </si>
-  <si>
-    <t>7.09%</t>
-  </si>
-  <si>
-    <t>5.52%</t>
-  </si>
-  <si>
-    <t>6.59%</t>
-  </si>
-  <si>
-    <t>7.06%</t>
-  </si>
-  <si>
-    <t>6.35%</t>
-  </si>
-  <si>
-    <t>6.33%</t>
-  </si>
-  <si>
-    <t>7.29%</t>
-  </si>
-  <si>
-    <t>8.38%</t>
-  </si>
-  <si>
-    <t>10.37%</t>
-  </si>
-  <si>
-    <t>8.98%</t>
-  </si>
-  <si>
-    <t>9.98%</t>
-  </si>
-  <si>
-    <t>11.10%</t>
-  </si>
-  <si>
-    <t>18.66%</t>
-  </si>
-  <si>
-    <t>15.74%</t>
-  </si>
-  <si>
-    <t>11.99%</t>
-  </si>
-  <si>
-    <t>17.96%</t>
-  </si>
-  <si>
-    <t>13.97%</t>
-  </si>
-  <si>
-    <t>17.16%</t>
-  </si>
-  <si>
-    <t>17.22%</t>
-  </si>
-  <si>
-    <t>18.85%</t>
-  </si>
-  <si>
-    <t>19.56%</t>
-  </si>
-  <si>
-    <t>20.50%</t>
-  </si>
-  <si>
-    <t>24.10%</t>
-  </si>
-  <si>
-    <t>28.60%</t>
-  </si>
-  <si>
-    <t>0.10%</t>
-  </si>
-  <si>
-    <t>0.21%</t>
-  </si>
-  <si>
-    <t>0.51%</t>
-  </si>
-  <si>
-    <t>0.55%</t>
-  </si>
-  <si>
-    <t>0.39%</t>
-  </si>
-  <si>
-    <t>0.30%</t>
-  </si>
-  <si>
-    <t>0.38%</t>
-  </si>
-  <si>
-    <t>0.43%</t>
-  </si>
-  <si>
-    <t>0.73%</t>
-  </si>
-  <si>
-    <t>0.37%</t>
-  </si>
-  <si>
-    <t>0.64%</t>
-  </si>
-  <si>
-    <t>0.67%</t>
-  </si>
-  <si>
-    <t>0.52%</t>
-  </si>
-  <si>
-    <t>0.91%</t>
-  </si>
-  <si>
-    <t>0.65%</t>
-  </si>
-  <si>
-    <t>1.02%</t>
-  </si>
-  <si>
-    <t>0.56%</t>
-  </si>
-  <si>
-    <t>0.66%</t>
-  </si>
-  <si>
-    <t>0.87%</t>
-  </si>
-  <si>
-    <t>1.25%</t>
-  </si>
-  <si>
-    <t>1.21%</t>
-  </si>
-  <si>
-    <t>0.93%</t>
-  </si>
-  <si>
-    <t>1.28%</t>
-  </si>
-  <si>
-    <t>1.29%</t>
-  </si>
-  <si>
-    <t>1.23%</t>
-  </si>
-  <si>
-    <t>1.10%</t>
-  </si>
-  <si>
-    <t>1.96%</t>
-  </si>
-  <si>
     <t>12.00%</t>
   </si>
   <si>
@@ -642,97 +555,91 @@
     <t>Explanation</t>
   </si>
   <si>
-    <t>NORMAL_VOL: 11.0% vol close to 12% target, scaling 1.09x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.6% vol close to 12% target, scaling 1.40x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 3.9% vol needs 3.1x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 5.2% vol needs 2.3x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.8% vol needs 2.5x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 6.5% vol close to 12% target, scaling 1.85x</t>
-  </si>
-  <si>
-    <t>HIGH_VOL: 21.4% vol needs 0.56x less capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>HIGH_VOL: 19.0% vol needs 0.63x less capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 11.2% vol close to 12% target, scaling 1.07x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 15.6% vol close to 12% target, scaling 0.77x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 6.1% vol close to 12% target, scaling 1.98x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 3.7% vol needs 3.2x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 12.8% vol close to 12% target, scaling 0.94x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.4% vol close to 12% target, scaling 1.44x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 12.2% vol close to 12% target, scaling 0.99x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 5.6% vol needs 2.2x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 17.8% vol close to 12% target, scaling 0.68x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 13.7% vol close to 12% target, scaling 0.87x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 12.2% vol close to 12% target, scaling 0.98x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 7.7% vol close to 12% target, scaling 1.55x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 1.8% vol needs 6.8x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.5% vol needs 2.7x more capital to reach 12% target</t>
+    <t>HIGH_VOL: 18.7% vol needs 0.64x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 9.0% vol close to 12% target, scaling 1.34x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 4.6% vol needs 2.6x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 7.1% vol close to 12% target, scaling 1.70x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 7.1% vol close to 12% target, scaling 1.69x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 7.3% vol close to 12% target, scaling 1.65x</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 28.6% vol needs 0.42x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 24.1% vol needs 0.50x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 15.7% vol close to 12% target, scaling 0.76x</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 19.6% vol needs 0.61x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 6.3% vol close to 12% target, scaling 1.90x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 5.5% vol needs 2.2x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 17.2% vol close to 12% target, scaling 0.70x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 10.4% vol close to 12% target, scaling 1.16x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 18.0% vol close to 12% target, scaling 0.67x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 6.3% vol close to 12% target, scaling 1.89x</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 20.5% vol needs 0.59x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>HIGH_VOL: 18.8% vol needs 0.64x less capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 14.0% vol close to 12% target, scaling 0.86x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 8.4% vol close to 12% target, scaling 1.43x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 1.7% vol needs 7.1x more capital to reach 12% target</t>
   </si>
   <si>
     <t>LOW_VOL: 4.3% vol needs 2.8x more capital to reach 12% target</t>
   </si>
   <si>
-    <t>LOW_VOL: 3.5% vol needs 3.4x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 1.8% vol needs 6.6x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.6% vol needs 2.6x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.9% vol close to 12% target, scaling 1.34x</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 12.5% vol close to 12% target, scaling 0.96x</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.9% vol needs 2.5x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>LOW_VOL: 4.9% vol needs 2.4x more capital to reach 12% target</t>
-  </si>
-  <si>
-    <t>NORMAL_VOL: 8.8% vol close to 12% target, scaling 1.36x</t>
+    <t>LOW_VOL: 5.4% vol needs 2.2x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 1.6% vol needs 7.6x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 12.0% vol close to 12% target, scaling 1.00x</t>
+  </si>
+  <si>
+    <t>LOW_VOL: 5.3% vol needs 2.3x more capital to reach 12% target</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 11.1% vol close to 12% target, scaling 1.08x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 6.6% vol close to 12% target, scaling 1.82x</t>
+  </si>
+  <si>
+    <t>NORMAL_VOL: 10.0% vol close to 12% target, scaling 1.20x</t>
   </si>
   <si>
     <t>Value</t>
@@ -1188,25 +1095,25 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>0.01762469926214086</v>
+        <v>0.01577993773301148</v>
       </c>
       <c r="C2">
-        <v>0.01659809158636668</v>
+        <v>0.03380592602919915</v>
       </c>
       <c r="D2">
-        <v>0.01833460187285361</v>
+        <v>0.01780062262726978</v>
       </c>
       <c r="E2">
-        <v>0.01679016279081553</v>
+        <v>0.01577993773301154</v>
       </c>
       <c r="F2">
-        <v>0.001045581489899995</v>
+        <v>0.002129573169369196</v>
       </c>
       <c r="G2">
         <v>0.12</v>
       </c>
       <c r="H2">
-        <v>6.808626814856849</v>
+        <v>7.604592744935943</v>
       </c>
       <c r="I2">
         <v>0.009096361455417834</v>
@@ -1227,19 +1134,19 @@
         <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q2" t="s">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="R2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="S2" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1247,25 +1154,25 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>0.01809404311665208</v>
+        <v>0.01679017434371363</v>
       </c>
       <c r="C3">
-        <v>0.03380599832475559</v>
+        <v>0.01659803311383836</v>
       </c>
       <c r="D3">
-        <v>0.0178006226272682</v>
+        <v>0.01833460187285357</v>
       </c>
       <c r="E3">
-        <v>0.01578008016422898</v>
+        <v>0.01679017434371359</v>
       </c>
       <c r="F3">
-        <v>0.002129577723561178</v>
+        <v>0.001045577806476937</v>
       </c>
       <c r="G3">
         <v>0.12</v>
       </c>
       <c r="H3">
-        <v>6.632016914426557</v>
+        <v>7.147037162537202</v>
       </c>
       <c r="I3">
         <v>0.009096361455417834</v>
@@ -1286,19 +1193,19 @@
         <v>52</v>
       </c>
       <c r="O3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q3" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="R3" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="S3" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1306,31 +1213,31 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>0.03502611942537402</v>
+        <v>0.04326590760205494</v>
       </c>
       <c r="C4">
-        <v>0.08175352354600299</v>
+        <v>0.04725191523450562</v>
       </c>
       <c r="D4">
-        <v>0.02681095546290775</v>
+        <v>0.04115602548720716</v>
       </c>
       <c r="E4">
-        <v>0.05448797335121321</v>
+        <v>0.04326590760205506</v>
       </c>
       <c r="F4">
-        <v>0.005149987907285411</v>
+        <v>0.002976590873381099</v>
       </c>
       <c r="G4">
         <v>0.12</v>
       </c>
       <c r="H4">
-        <v>3.426014698992554</v>
+        <v>2.773546347477997</v>
       </c>
       <c r="I4">
-        <v>0.005497800879648141</v>
+        <v>0.009096361455417834</v>
       </c>
       <c r="J4">
-        <v>0.005497800879682417</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K4">
         <v>1.000000000006235</v>
@@ -1345,19 +1252,19 @@
         <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q4" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="R4" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="S4" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1365,31 +1272,31 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>0.03694532067208307</v>
+        <v>0.04596450331930595</v>
       </c>
       <c r="C5">
-        <v>0.08782984444390952</v>
+        <v>0.05968641391814792</v>
       </c>
       <c r="D5">
-        <v>0.02726544361215556</v>
+        <v>0.04124612217863124</v>
       </c>
       <c r="E5">
-        <v>0.05500660148161585</v>
+        <v>0.04596450331930572</v>
       </c>
       <c r="F5">
-        <v>0.005532760144954111</v>
+        <v>0.003759890663730564</v>
       </c>
       <c r="G5">
         <v>0.12</v>
       </c>
       <c r="H5">
-        <v>3.248043265481125</v>
+        <v>2.610710251047089</v>
       </c>
       <c r="I5">
-        <v>0.005497800879648141</v>
+        <v>0.01009596161535386</v>
       </c>
       <c r="J5">
-        <v>0.005497800879682417</v>
+        <v>0.0100959616154168</v>
       </c>
       <c r="K5">
         <v>1.000000000006235</v>
@@ -1404,19 +1311,19 @@
         <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q5" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="R5" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="S5" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1424,25 +1331,25 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>0.03914619504344222</v>
+        <v>0.04603204955314132</v>
       </c>
       <c r="C6">
-        <v>0.06127978794129803</v>
+        <v>0.06127977382701655</v>
       </c>
       <c r="D6">
-        <v>0.03906767639849132</v>
+        <v>0.0390676763984908</v>
       </c>
       <c r="E6">
-        <v>0.04603199891185989</v>
+        <v>0.04603204955314152</v>
       </c>
       <c r="F6">
-        <v>0.003860263792558318</v>
+        <v>0.003860262903442157</v>
       </c>
       <c r="G6">
         <v>0.12</v>
       </c>
       <c r="H6">
-        <v>3.065432026454444</v>
+        <v>2.606879362637698</v>
       </c>
       <c r="I6">
         <v>0.005497800879648141</v>
@@ -1460,22 +1367,22 @@
         <v>1989</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="Q6" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="S6" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1483,25 +1390,25 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>0.0425423662168037</v>
+        <v>0.0527875100871464</v>
       </c>
       <c r="C7">
-        <v>0.04725179619000613</v>
+        <v>0.06753543710174584</v>
       </c>
       <c r="D7">
-        <v>0.04115602548720683</v>
+        <v>0.04286117691899426</v>
       </c>
       <c r="E7">
-        <v>0.04326591465460872</v>
+        <v>0.05278751008714633</v>
       </c>
       <c r="F7">
-        <v>0.002976583374282513</v>
+        <v>0.004254332648934863</v>
       </c>
       <c r="G7">
         <v>0.12</v>
       </c>
       <c r="H7">
-        <v>2.820717573358708</v>
+        <v>2.273265016703632</v>
       </c>
       <c r="I7">
         <v>0.009096361455417834</v>
@@ -1519,22 +1426,22 @@
         <v>1989</v>
       </c>
       <c r="N7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q7" t="s">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="R7" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="S7" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1542,31 +1449,31 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>0.04523816926953131</v>
+        <v>0.05448790929355872</v>
       </c>
       <c r="C8">
-        <v>0.05968642054957227</v>
+        <v>0.08175345879296146</v>
       </c>
       <c r="D8">
-        <v>0.04124612217863163</v>
+        <v>0.02681095546290673</v>
       </c>
       <c r="E8">
-        <v>0.04596450143136226</v>
+        <v>0.0544879092935587</v>
       </c>
       <c r="F8">
-        <v>0.003759891081471032</v>
+        <v>0.005149983828227209</v>
       </c>
       <c r="G8">
         <v>0.12</v>
       </c>
       <c r="H8">
-        <v>2.652627237964337</v>
+        <v>2.202323443050251</v>
       </c>
       <c r="I8">
-        <v>0.01009596161535386</v>
+        <v>0.005497800879648141</v>
       </c>
       <c r="J8">
-        <v>0.0100959616154168</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K8">
         <v>1.000000000006235</v>
@@ -1578,22 +1485,22 @@
         <v>1989</v>
       </c>
       <c r="N8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P8" t="s">
         <v>117</v>
       </c>
       <c r="Q8" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="R8" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="S8" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1601,31 +1508,31 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>0.04551625614122628</v>
+        <v>0.05500661444164982</v>
       </c>
       <c r="C9">
-        <v>0.06753532939207312</v>
+        <v>0.0878298855256803</v>
       </c>
       <c r="D9">
-        <v>0.04286117691899444</v>
+        <v>0.02726544361216034</v>
       </c>
       <c r="E9">
-        <v>0.05278748843208499</v>
+        <v>0.05500661444165003</v>
       </c>
       <c r="F9">
-        <v>0.004254325863863248</v>
+        <v>0.005532762732862418</v>
       </c>
       <c r="G9">
         <v>0.12</v>
       </c>
       <c r="H9">
-        <v>2.636420702697254</v>
+        <v>2.181555822296501</v>
       </c>
       <c r="I9">
-        <v>0.009096361455417834</v>
+        <v>0.005497800879648141</v>
       </c>
       <c r="J9">
-        <v>0.009096361455474546</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K9">
         <v>1.000000000006235</v>
@@ -1637,22 +1544,22 @@
         <v>1989</v>
       </c>
       <c r="N9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P9" t="s">
         <v>118</v>
       </c>
       <c r="Q9" t="s">
-        <v>148</v>
+        <v>57</v>
       </c>
       <c r="R9" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="S9" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1660,31 +1567,31 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>0.04770117265223589</v>
+        <v>0.05523231249676754</v>
       </c>
       <c r="C10">
-        <v>0.1158112727183454</v>
+        <v>0.05820631743817728</v>
       </c>
       <c r="D10">
-        <v>0.03925305962803242</v>
+        <v>0.04643763892460204</v>
       </c>
       <c r="E10">
-        <v>0.07088242212865427</v>
+        <v>0.05523231249676765</v>
       </c>
       <c r="F10">
-        <v>0.007295424443586221</v>
+        <v>0.003666653349388078</v>
       </c>
       <c r="G10">
         <v>0.12</v>
       </c>
       <c r="H10">
-        <v>2.515661425660471</v>
+        <v>2.172641241610569</v>
       </c>
       <c r="I10">
-        <v>0.01859256297481008</v>
+        <v>0.007297081167532987</v>
       </c>
       <c r="J10">
-        <v>0.01859256297492599</v>
+        <v>0.007297081167578481</v>
       </c>
       <c r="K10">
         <v>1.000000000006235</v>
@@ -1696,22 +1603,22 @@
         <v>1989</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P10" t="s">
         <v>119</v>
       </c>
       <c r="Q10" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="R10" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="S10" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1719,34 +1626,34 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.04853638764815744</v>
+        <v>0.06327840262463671</v>
       </c>
       <c r="C11">
-        <v>0.05820630130771236</v>
+        <v>0.144377403980939</v>
       </c>
       <c r="D11">
-        <v>0.04643763892460204</v>
+        <v>0.04764462380119413</v>
       </c>
       <c r="E11">
-        <v>0.05523233757399295</v>
+        <v>0.06327840262463988</v>
       </c>
       <c r="F11">
-        <v>0.003666652333264299</v>
+        <v>0.009094921568349321</v>
       </c>
       <c r="G11">
         <v>0.12</v>
       </c>
       <c r="H11">
-        <v>2.472371880451542</v>
+        <v>1.896381625051948</v>
       </c>
       <c r="I11">
         <v>0.007297081167532987</v>
       </c>
       <c r="J11">
-        <v>0.007297081167578481</v>
+        <v>0.007297081167111755</v>
       </c>
       <c r="K11">
-        <v>1.000000000006235</v>
+        <v>0.999999999942274</v>
       </c>
       <c r="L11" t="s">
         <v>50</v>
@@ -1755,22 +1662,22 @@
         <v>1989</v>
       </c>
       <c r="N11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P11" t="s">
         <v>120</v>
       </c>
       <c r="Q11" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="R11" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="S11" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1778,31 +1685,31 @@
         <v>28</v>
       </c>
       <c r="B12">
-        <v>0.04935812195542288</v>
+        <v>0.06349041481209834</v>
       </c>
       <c r="C12">
-        <v>0.1008416194848006</v>
+        <v>0.08178541728223565</v>
       </c>
       <c r="D12">
-        <v>0.04306628604415293</v>
+        <v>0.056093072190617</v>
       </c>
       <c r="E12">
-        <v>0.06594999924372404</v>
+        <v>0.06349041481209852</v>
       </c>
       <c r="F12">
-        <v>0.006352424927661615</v>
+        <v>0.00515199702381999</v>
       </c>
       <c r="G12">
         <v>0.12</v>
       </c>
       <c r="H12">
-        <v>2.431210816902158</v>
+        <v>1.890049078355266</v>
       </c>
       <c r="I12">
-        <v>0.02479008396641344</v>
+        <v>0.06377449020391843</v>
       </c>
       <c r="J12">
-        <v>0.02479008396656799</v>
+        <v>0.06377449020431604</v>
       </c>
       <c r="K12">
         <v>1.000000000006235</v>
@@ -1814,22 +1721,22 @@
         <v>1989</v>
       </c>
       <c r="N12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="P12" t="s">
         <v>121</v>
       </c>
       <c r="Q12" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="R12" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="S12" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1837,31 +1744,31 @@
         <v>29</v>
       </c>
       <c r="B13">
-        <v>0.05181018488653797</v>
+        <v>0.06594985582618719</v>
       </c>
       <c r="C13">
-        <v>0.1070007691823626</v>
+        <v>0.1008418200656166</v>
       </c>
       <c r="D13">
-        <v>0.04504281680683247</v>
+        <v>0.04306628604415387</v>
       </c>
       <c r="E13">
-        <v>0.07059593803018702</v>
+        <v>0.06594985582618762</v>
       </c>
       <c r="F13">
-        <v>0.006740414889265607</v>
+        <v>0.006352437563065349</v>
       </c>
       <c r="G13">
         <v>0.12</v>
       </c>
       <c r="H13">
-        <v>2.316146917112817</v>
+        <v>1.819564250697736</v>
       </c>
       <c r="I13">
-        <v>0.0505797680927629</v>
+        <v>0.02479008396641344</v>
       </c>
       <c r="J13">
-        <v>0.05057976809307824</v>
+        <v>0.02479008396656799</v>
       </c>
       <c r="K13">
         <v>1.000000000006235</v>
@@ -1873,22 +1780,22 @@
         <v>1989</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P13" t="s">
         <v>122</v>
       </c>
       <c r="Q13" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="R13" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="S13" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1896,31 +1803,31 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>0.05563680009278063</v>
+        <v>0.07059608949622291</v>
       </c>
       <c r="C14">
-        <v>0.08178553433194409</v>
+        <v>0.1070007327399687</v>
       </c>
       <c r="D14">
-        <v>0.05609307219061594</v>
+        <v>0.04504281680683441</v>
       </c>
       <c r="E14">
-        <v>0.06349039923138614</v>
+        <v>0.07059608949622287</v>
       </c>
       <c r="F14">
-        <v>0.005152004397258552</v>
+        <v>0.006740412593610572</v>
       </c>
       <c r="G14">
         <v>0.12</v>
       </c>
       <c r="H14">
-        <v>2.156845825063384</v>
+        <v>1.699810865677204</v>
       </c>
       <c r="I14">
-        <v>0.06377449020391843</v>
+        <v>0.0505797680927629</v>
       </c>
       <c r="J14">
-        <v>0.06377449020431604</v>
+        <v>0.05057976809307824</v>
       </c>
       <c r="K14">
         <v>1.000000000006235</v>
@@ -1932,22 +1839,22 @@
         <v>1989</v>
       </c>
       <c r="N14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O14" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="P14" t="s">
         <v>123</v>
       </c>
       <c r="Q14" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="R14" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="S14" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1955,34 +1862,34 @@
         <v>31</v>
       </c>
       <c r="B15">
-        <v>0.06067006888567235</v>
+        <v>0.07088224367916628</v>
       </c>
       <c r="C15">
-        <v>0.144377250250269</v>
+        <v>0.1158112997215818</v>
       </c>
       <c r="D15">
-        <v>0.04764462380120212</v>
+        <v>0.03925305962803229</v>
       </c>
       <c r="E15">
-        <v>0.06327827101454939</v>
+        <v>0.07088224367916617</v>
       </c>
       <c r="F15">
-        <v>0.009094911884227376</v>
+        <v>0.00729542614463022</v>
       </c>
       <c r="G15">
         <v>0.12</v>
       </c>
       <c r="H15">
-        <v>1.977911055715627</v>
+        <v>1.692948667696737</v>
       </c>
       <c r="I15">
-        <v>0.007297081167532987</v>
+        <v>0.01859256297481008</v>
       </c>
       <c r="J15">
-        <v>0.007297081167111755</v>
+        <v>0.01859256297492599</v>
       </c>
       <c r="K15">
-        <v>0.999999999942274</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L15" t="s">
         <v>50</v>
@@ -1991,22 +1898,22 @@
         <v>1989</v>
       </c>
       <c r="N15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P15" t="s">
         <v>124</v>
       </c>
       <c r="Q15" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="R15" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="S15" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2014,25 +1921,25 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>0.06469555905163277</v>
+        <v>0.07287077570905091</v>
       </c>
       <c r="C16">
-        <v>0.1010380446026012</v>
+        <v>0.1010378792941858</v>
       </c>
       <c r="D16">
-        <v>0.05901992590618146</v>
+        <v>0.0590199259061809</v>
       </c>
       <c r="E16">
-        <v>0.07287076127637157</v>
+        <v>0.07287077570905078</v>
       </c>
       <c r="F16">
-        <v>0.006364798547017493</v>
+        <v>0.006364788133566139</v>
       </c>
       <c r="G16">
         <v>0.12</v>
       </c>
       <c r="H16">
-        <v>1.85484137951771</v>
+        <v>1.646750687533787</v>
       </c>
       <c r="I16">
         <v>0.01859256297481008</v>
@@ -2050,22 +1957,22 @@
         <v>1989</v>
       </c>
       <c r="N16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P16" t="s">
         <v>125</v>
       </c>
       <c r="Q16" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="R16" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="S16" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2073,25 +1980,25 @@
         <v>33</v>
       </c>
       <c r="B17">
-        <v>0.07745530214105066</v>
+        <v>0.08383939575778916</v>
       </c>
       <c r="C17">
-        <v>0.1033261756230675</v>
+        <v>0.1033261279439506</v>
       </c>
       <c r="D17">
-        <v>0.07314772014172524</v>
+        <v>0.07314772014172588</v>
       </c>
       <c r="E17">
-        <v>0.08383944071938246</v>
+        <v>0.08383939575778913</v>
       </c>
       <c r="F17">
-        <v>0.00650893725290526</v>
+        <v>0.006508934249403213</v>
       </c>
       <c r="G17">
         <v>0.12</v>
       </c>
       <c r="H17">
-        <v>1.54928063906423</v>
+        <v>1.431308025485755</v>
       </c>
       <c r="I17">
         <v>0.06377449020391843</v>
@@ -2109,22 +2016,22 @@
         <v>1989</v>
       </c>
       <c r="N17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P17" t="s">
         <v>126</v>
       </c>
       <c r="Q17" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="R17" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="S17" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2132,31 +2039,31 @@
         <v>34</v>
       </c>
       <c r="B18">
-        <v>0.08358202127746187</v>
+        <v>0.08975780554626052</v>
       </c>
       <c r="C18">
-        <v>0.1625931982412989</v>
+        <v>0.08877909725199067</v>
       </c>
       <c r="D18">
-        <v>0.07221056611840437</v>
+        <v>0.08556501897225192</v>
       </c>
       <c r="E18">
-        <v>0.1036988113042716</v>
+        <v>0.08975780554626074</v>
       </c>
       <c r="F18">
-        <v>0.01024240874802622</v>
+        <v>0.005592557451180597</v>
       </c>
       <c r="G18">
         <v>0.12</v>
       </c>
       <c r="H18">
-        <v>1.435715458491291</v>
+        <v>1.336931081031753</v>
       </c>
       <c r="I18">
-        <v>0.005497800879648141</v>
+        <v>0.08506597361055578</v>
       </c>
       <c r="J18">
-        <v>0.005497800879682417</v>
+        <v>0.08506597361108613</v>
       </c>
       <c r="K18">
         <v>1.000000000006235</v>
@@ -2168,22 +2075,22 @@
         <v>1989</v>
       </c>
       <c r="N18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P18" t="s">
         <v>127</v>
       </c>
       <c r="Q18" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="R18" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="S18" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2191,31 +2098,31 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>0.08599260288294111</v>
+        <v>0.09983316117581224</v>
       </c>
       <c r="C19">
-        <v>0.08877909105670397</v>
+        <v>0.1052790626488503</v>
       </c>
       <c r="D19">
-        <v>0.0855650189722526</v>
+        <v>0.08149139309562857</v>
       </c>
       <c r="E19">
-        <v>0.08975810484614052</v>
+        <v>0.09983316117581227</v>
       </c>
       <c r="F19">
-        <v>0.005592557060914219</v>
+        <v>0.006631957572163021</v>
       </c>
       <c r="G19">
         <v>0.12</v>
       </c>
       <c r="H19">
-        <v>1.395468865657573</v>
+        <v>1.202005411695546</v>
       </c>
       <c r="I19">
-        <v>0.08506597361055578</v>
+        <v>0.0235905637744902</v>
       </c>
       <c r="J19">
-        <v>0.08506597361108613</v>
+        <v>0.02359056377463728</v>
       </c>
       <c r="K19">
         <v>1.000000000006235</v>
@@ -2227,22 +2134,22 @@
         <v>1989</v>
       </c>
       <c r="N19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P19" t="s">
         <v>128</v>
       </c>
       <c r="Q19" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="R19" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="S19" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2250,31 +2157,31 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>0.08795103108520301</v>
+        <v>0.1036987369168453</v>
       </c>
       <c r="C20">
-        <v>0.1052790455646434</v>
+        <v>0.1625931928391213</v>
       </c>
       <c r="D20">
-        <v>0.08149139309562874</v>
+        <v>0.07221056611840493</v>
       </c>
       <c r="E20">
-        <v>0.09983301538084144</v>
+        <v>0.1036987369168454</v>
       </c>
       <c r="F20">
-        <v>0.006631956495959142</v>
+        <v>0.01024240840772102</v>
       </c>
       <c r="G20">
         <v>0.12</v>
       </c>
       <c r="H20">
-        <v>1.364395601954335</v>
+        <v>1.157198280015951</v>
       </c>
       <c r="I20">
-        <v>0.0235905637744902</v>
+        <v>0.005497800879648141</v>
       </c>
       <c r="J20">
-        <v>0.02359056377463728</v>
+        <v>0.005497800879682417</v>
       </c>
       <c r="K20">
         <v>1.000000000006235</v>
@@ -2286,22 +2193,22 @@
         <v>1989</v>
       </c>
       <c r="N20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P20" t="s">
         <v>129</v>
       </c>
       <c r="Q20" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="R20" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="S20" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2309,25 +2216,25 @@
         <v>37</v>
       </c>
       <c r="B21">
-        <v>0.0893857405791231</v>
+        <v>0.1109873177583198</v>
       </c>
       <c r="C21">
-        <v>0.1380233989343314</v>
+        <v>0.1380232693908942</v>
       </c>
       <c r="D21">
-        <v>0.08185506902534645</v>
+        <v>0.08185506902534524</v>
       </c>
       <c r="E21">
-        <v>0.1109874221455964</v>
+        <v>0.1109873177583199</v>
       </c>
       <c r="F21">
-        <v>0.008694656873526148</v>
+        <v>0.008694648713056655</v>
       </c>
       <c r="G21">
         <v>0.12</v>
       </c>
       <c r="H21">
-        <v>1.342496009123262</v>
+        <v>1.081204613497425</v>
       </c>
       <c r="I21">
         <v>0.009096361455417834</v>
@@ -2345,22 +2252,22 @@
         <v>1989</v>
       </c>
       <c r="N21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P21" t="s">
         <v>130</v>
       </c>
       <c r="Q21" t="s">
-        <v>160</v>
+        <v>69</v>
       </c>
       <c r="R21" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="S21" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2368,58 +2275,58 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>0.110051083502396</v>
+        <v>0.1199080515509558</v>
       </c>
       <c r="C22">
-        <v>0.197681324065112</v>
+        <v>0.1469196686909274</v>
       </c>
       <c r="D22">
-        <v>0.1070746296339144</v>
+        <v>0.104903417863623</v>
       </c>
       <c r="E22">
-        <v>0.1865964815001218</v>
+        <v>0.1199080515509558</v>
       </c>
       <c r="F22">
-        <v>0.01245275291233939</v>
+        <v>0.009255069191909439</v>
       </c>
       <c r="G22">
         <v>0.12</v>
       </c>
       <c r="H22">
-        <v>1.090402712821882</v>
+        <v>1.000766824644841</v>
       </c>
       <c r="I22">
-        <v>0.06747301079568173</v>
+        <v>0.009096361455417834</v>
       </c>
       <c r="J22">
-        <v>0.0674730107960885</v>
+        <v>0.009096361455474546</v>
       </c>
       <c r="K22">
-        <v>1.000000000006029</v>
+        <v>1.000000000006235</v>
       </c>
       <c r="L22" t="s">
         <v>50</v>
       </c>
       <c r="M22">
-        <v>1832</v>
+        <v>1989</v>
       </c>
       <c r="N22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P22" t="s">
         <v>131</v>
       </c>
       <c r="Q22" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="S22" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2427,31 +2334,31 @@
         <v>39</v>
       </c>
       <c r="B23">
-        <v>0.1120818178495579</v>
+        <v>0.1396733541100288</v>
       </c>
       <c r="C23">
-        <v>0.1923590970756769</v>
+        <v>0.2047897320304424</v>
       </c>
       <c r="D23">
-        <v>0.1098680696991763</v>
+        <v>0.09543738975822261</v>
       </c>
       <c r="E23">
-        <v>0.1573947913173102</v>
+        <v>0.1396733541100296</v>
       </c>
       <c r="F23">
-        <v>0.01211748412578983</v>
+        <v>0.01290054052409784</v>
       </c>
       <c r="G23">
         <v>0.12</v>
       </c>
       <c r="H23">
-        <v>1.070646446518831</v>
+        <v>0.8591474069239362</v>
       </c>
       <c r="I23">
-        <v>0.02249100359856058</v>
+        <v>0.01129548180727709</v>
       </c>
       <c r="J23">
-        <v>0.0224910035987008</v>
+        <v>0.01129548180734751</v>
       </c>
       <c r="K23">
         <v>1.000000000006235</v>
@@ -2463,22 +2370,22 @@
         <v>1989</v>
       </c>
       <c r="N23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P23" t="s">
         <v>132</v>
       </c>
       <c r="Q23" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="R23" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="S23" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2486,31 +2393,31 @@
         <v>40</v>
       </c>
       <c r="B24">
-        <v>0.1215164053503871</v>
+        <v>0.1573947913173104</v>
       </c>
       <c r="C24">
-        <v>0.1469195459028001</v>
+        <v>0.1923591312026382</v>
       </c>
       <c r="D24">
-        <v>0.104903417863623</v>
+        <v>0.1098680696991744</v>
       </c>
       <c r="E24">
-        <v>0.1199080792781482</v>
+        <v>0.1573947913173107</v>
       </c>
       <c r="F24">
-        <v>0.009255061456984466</v>
+        <v>0.01211748627558632</v>
       </c>
       <c r="G24">
         <v>0.12</v>
       </c>
       <c r="H24">
-        <v>0.9875209824877997</v>
+        <v>0.7624140481121647</v>
       </c>
       <c r="I24">
-        <v>0.009096361455417834</v>
+        <v>0.02249100359856058</v>
       </c>
       <c r="J24">
-        <v>0.009096361455474546</v>
+        <v>0.0224910035987008</v>
       </c>
       <c r="K24">
         <v>1.000000000006235</v>
@@ -2522,22 +2429,22 @@
         <v>1989</v>
       </c>
       <c r="N24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P24" t="s">
         <v>133</v>
       </c>
       <c r="Q24" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="R24" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="S24" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2545,31 +2452,31 @@
         <v>41</v>
       </c>
       <c r="B25">
-        <v>0.1217349660257986</v>
+        <v>0.1715950485483466</v>
       </c>
       <c r="C25">
-        <v>0.2039807001655037</v>
+        <v>0.1954580184062897</v>
       </c>
       <c r="D25">
-        <v>0.1080689037661476</v>
+        <v>0.1373197523201179</v>
       </c>
       <c r="E25">
-        <v>0.179605286423776</v>
+        <v>0.1715950485483465</v>
       </c>
       <c r="F25">
-        <v>0.01284957630701797</v>
+        <v>0.01231269782039352</v>
       </c>
       <c r="G25">
         <v>0.12</v>
       </c>
       <c r="H25">
-        <v>0.985748005832351</v>
+        <v>0.6993208779342501</v>
       </c>
       <c r="I25">
-        <v>0.04498200719712115</v>
+        <v>0.1124550179928029</v>
       </c>
       <c r="J25">
-        <v>0.04498200719740159</v>
+        <v>0.112455017993504</v>
       </c>
       <c r="K25">
         <v>1.000000000006235</v>
@@ -2581,22 +2488,22 @@
         <v>1989</v>
       </c>
       <c r="N25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P25" t="s">
         <v>134</v>
       </c>
       <c r="Q25" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="R25" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="S25" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -2604,31 +2511,31 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>0.1221898841733612</v>
+        <v>0.1722147369141073</v>
       </c>
       <c r="C26">
-        <v>0.2047897038702714</v>
+        <v>0.1442774328087733</v>
       </c>
       <c r="D26">
-        <v>0.09543738975822265</v>
+        <v>0.1337337072847106</v>
       </c>
       <c r="E26">
-        <v>0.1396733077830793</v>
+        <v>0.1722147369141076</v>
       </c>
       <c r="F26">
-        <v>0.01290053875017381</v>
+        <v>0.0090886239764487</v>
       </c>
       <c r="G26">
         <v>0.12</v>
       </c>
       <c r="H26">
-        <v>0.9820780239855681</v>
+        <v>0.6968044788167601</v>
       </c>
       <c r="I26">
-        <v>0.01129548180727709</v>
+        <v>0.09996001599360257</v>
       </c>
       <c r="J26">
-        <v>0.01129548180734751</v>
+        <v>0.09996001599422578</v>
       </c>
       <c r="K26">
         <v>1.000000000006235</v>
@@ -2640,22 +2547,22 @@
         <v>1989</v>
       </c>
       <c r="N26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P26" t="s">
         <v>135</v>
       </c>
       <c r="Q26" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="R26" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="S26" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2663,31 +2570,31 @@
         <v>43</v>
       </c>
       <c r="B27">
-        <v>0.1246924739119454</v>
+        <v>0.179605306105785</v>
       </c>
       <c r="C27">
-        <v>0.1954580125518941</v>
+        <v>0.2039807273076665</v>
       </c>
       <c r="D27">
-        <v>0.1373197523201167</v>
+        <v>0.1080689037661465</v>
       </c>
       <c r="E27">
-        <v>0.171595041647547</v>
+        <v>0.1796053061057847</v>
       </c>
       <c r="F27">
-        <v>0.01231269745160126</v>
+        <v>0.01284957801681351</v>
       </c>
       <c r="G27">
         <v>0.12</v>
       </c>
       <c r="H27">
-        <v>0.9623676252084058</v>
+        <v>0.6681317083656853</v>
       </c>
       <c r="I27">
-        <v>0.1124550179928029</v>
+        <v>0.04498200719712115</v>
       </c>
       <c r="J27">
-        <v>0.112455017993504</v>
+        <v>0.04498200719740159</v>
       </c>
       <c r="K27">
         <v>1.000000000006235</v>
@@ -2699,22 +2606,22 @@
         <v>1989</v>
       </c>
       <c r="N27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="Q27" t="s">
+        <v>75</v>
+      </c>
+      <c r="R27" t="s">
         <v>166</v>
       </c>
-      <c r="R27" t="s">
-        <v>197</v>
-      </c>
       <c r="S27" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2722,58 +2629,58 @@
         <v>44</v>
       </c>
       <c r="B28">
-        <v>0.1282260148058714</v>
+        <v>0.1865964563170754</v>
       </c>
       <c r="C28">
-        <v>0.1442774328087733</v>
+        <v>0.1976812769404888</v>
       </c>
       <c r="D28">
-        <v>0.1337337072847106</v>
+        <v>0.1070746296339154</v>
       </c>
       <c r="E28">
-        <v>0.1722147369141076</v>
+        <v>0.1865964563170753</v>
       </c>
       <c r="F28">
-        <v>0.0090886239764487</v>
+        <v>0.01245274994376716</v>
       </c>
       <c r="G28">
         <v>0.12</v>
       </c>
       <c r="H28">
-        <v>0.9358475359440496</v>
+        <v>0.6430990296840853</v>
       </c>
       <c r="I28">
-        <v>0.09996001599360257</v>
+        <v>0.06747301079568173</v>
       </c>
       <c r="J28">
-        <v>0.09996001599422578</v>
+        <v>0.0674730107960885</v>
       </c>
       <c r="K28">
-        <v>1.000000000006235</v>
+        <v>1.000000000006029</v>
       </c>
       <c r="L28" t="s">
         <v>50</v>
       </c>
       <c r="M28">
-        <v>1989</v>
+        <v>1832</v>
       </c>
       <c r="N28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q28" t="s">
+        <v>76</v>
+      </c>
+      <c r="R28" t="s">
         <v>167</v>
       </c>
-      <c r="R28" t="s">
-        <v>186</v>
-      </c>
       <c r="S28" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2781,25 +2688,25 @@
         <v>45</v>
       </c>
       <c r="B29">
-        <v>0.1373249102743785</v>
+        <v>0.1884552982763563</v>
       </c>
       <c r="C29">
-        <v>0.1955329061894823</v>
+        <v>0.1955328862574739</v>
       </c>
       <c r="D29">
-        <v>0.09471487952081561</v>
+        <v>0.09471487952081481</v>
       </c>
       <c r="E29">
-        <v>0.1884552852954027</v>
+        <v>0.1884552982763557</v>
       </c>
       <c r="F29">
-        <v>0.01231741530731172</v>
+        <v>0.01231741405171322</v>
       </c>
       <c r="G29">
         <v>0.12</v>
       </c>
       <c r="H29">
-        <v>0.873840002955306</v>
+        <v>0.6367557776169739</v>
       </c>
       <c r="I29">
         <v>0.0899640143942423</v>
@@ -2817,22 +2724,22 @@
         <v>1989</v>
       </c>
       <c r="N29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O29" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q29" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="R29" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="S29" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2840,25 +2747,25 @@
         <v>46</v>
       </c>
       <c r="B30">
-        <v>0.1556175660677405</v>
+        <v>0.1956137069476524</v>
       </c>
       <c r="C30">
-        <v>0.1744036900446199</v>
+        <v>0.174403673133883</v>
       </c>
       <c r="D30">
-        <v>0.203790975500498</v>
+        <v>0.2037909755004981</v>
       </c>
       <c r="E30">
-        <v>0.1956137069476523</v>
+        <v>0.1956137069476522</v>
       </c>
       <c r="F30">
-        <v>0.01098639979976323</v>
+        <v>0.01098639873448694</v>
       </c>
       <c r="G30">
         <v>0.12</v>
       </c>
       <c r="H30">
-        <v>0.7711211724501835</v>
+        <v>0.6134539438594291</v>
       </c>
       <c r="I30">
         <v>0.04498200719712115</v>
@@ -2876,22 +2783,22 @@
         <v>1989</v>
       </c>
       <c r="N30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q30" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="S30" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -2899,25 +2806,25 @@
         <v>47</v>
       </c>
       <c r="B31">
-        <v>0.1777624223750275</v>
+        <v>0.2049949555736961</v>
       </c>
       <c r="C31">
-        <v>0.2905093239436632</v>
+        <v>0.2905094125848296</v>
       </c>
       <c r="D31">
-        <v>0.1728541198957731</v>
+        <v>0.1728541198957751</v>
       </c>
       <c r="E31">
-        <v>0.2049949555736964</v>
+        <v>0.2049949555736954</v>
       </c>
       <c r="F31">
-        <v>0.01830036725477225</v>
+        <v>0.01830037283864088</v>
       </c>
       <c r="G31">
         <v>0.12</v>
       </c>
       <c r="H31">
-        <v>0.6750583075810845</v>
+        <v>0.5853802580857154</v>
       </c>
       <c r="I31">
         <v>0.03378648540583766</v>
@@ -2935,22 +2842,22 @@
         <v>1989</v>
       </c>
       <c r="N31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q31" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="R31" t="s">
         <v>113</v>
       </c>
       <c r="S31" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2958,25 +2865,25 @@
         <v>48</v>
       </c>
       <c r="B32">
-        <v>0.189993640881627</v>
+        <v>0.2409868301034742</v>
       </c>
       <c r="C32">
-        <v>0.3117674773473902</v>
+        <v>0.3117674384094113</v>
       </c>
       <c r="D32">
-        <v>0.1989134843737963</v>
+        <v>0.1989134843737968</v>
       </c>
       <c r="E32">
-        <v>0.2409867847174416</v>
+        <v>0.240986830103475</v>
       </c>
       <c r="F32">
-        <v>0.01963950504617042</v>
+        <v>0.01963950259330831</v>
       </c>
       <c r="G32">
         <v>0.12</v>
       </c>
       <c r="H32">
-        <v>0.6316000864195471</v>
+        <v>0.4979525227518646</v>
       </c>
       <c r="I32">
         <v>0.01129548180727709</v>
@@ -2994,22 +2901,22 @@
         <v>1989</v>
       </c>
       <c r="N32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q32" t="s">
+        <v>80</v>
+      </c>
+      <c r="R32" t="s">
+        <v>169</v>
+      </c>
+      <c r="S32" t="s">
         <v>171</v>
-      </c>
-      <c r="R32" t="s">
-        <v>199</v>
-      </c>
-      <c r="S32" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -3017,25 +2924,25 @@
         <v>49</v>
       </c>
       <c r="B33">
-        <v>0.2144832259760696</v>
+        <v>0.2859915458182896</v>
       </c>
       <c r="C33">
-        <v>0.2866675517735738</v>
+        <v>0.2866675459633484</v>
       </c>
       <c r="D33">
-        <v>0.2344223700902283</v>
+        <v>0.2344223700902282</v>
       </c>
       <c r="E33">
-        <v>0.2859915458182898</v>
+        <v>0.2859915458182896</v>
       </c>
       <c r="F33">
-        <v>0.01805835835582403</v>
+        <v>0.01805835798981423</v>
       </c>
       <c r="G33">
         <v>0.12</v>
       </c>
       <c r="H33">
-        <v>0.5594843114369636</v>
+        <v>0.4195928227761124</v>
       </c>
       <c r="I33">
         <v>0.01129548180727709</v>
@@ -3053,22 +2960,22 @@
         <v>1989</v>
       </c>
       <c r="N33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q33" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="R33" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="S33" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3087,86 +2994,86 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>0.06747301079568173</v>
       </c>
       <c r="C2">
-        <v>0.110051083502396</v>
+        <v>0.1865964563170754</v>
       </c>
       <c r="D2">
         <v>0.12</v>
       </c>
       <c r="E2">
-        <v>1.090402712821882</v>
+        <v>0.6430990296840853</v>
       </c>
       <c r="F2">
-        <v>0.07357275401387146</v>
+        <v>0.04339182777256673</v>
       </c>
       <c r="G2">
         <v>0.0674730107960885</v>
       </c>
       <c r="H2">
-        <v>0.006099743217782963</v>
+        <v>0.02408118302352177</v>
       </c>
       <c r="I2" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>0.08506597361055578</v>
       </c>
       <c r="C3">
-        <v>0.08599260288294111</v>
+        <v>0.08975780554626052</v>
       </c>
       <c r="D3">
         <v>0.12</v>
       </c>
       <c r="E3">
-        <v>1.395468865657573</v>
+        <v>1.336931081031753</v>
       </c>
       <c r="F3">
-        <v>0.1187069177003793</v>
+        <v>0.1137273440581789</v>
       </c>
       <c r="G3">
         <v>0.08506597361108613</v>
       </c>
       <c r="H3">
-        <v>0.0336409440892932</v>
+        <v>0.02866137044709281</v>
       </c>
       <c r="I3" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3177,83 +3084,83 @@
         <v>0.005497800879648141</v>
       </c>
       <c r="C4">
-        <v>0.03914619504344222</v>
+        <v>0.04603204955314132</v>
       </c>
       <c r="D4">
         <v>0.12</v>
       </c>
       <c r="E4">
-        <v>3.065432026454444</v>
+        <v>2.606879362637698</v>
       </c>
       <c r="F4">
-        <v>0.01685313489154282</v>
+        <v>0.01433210365304612</v>
       </c>
       <c r="G4">
         <v>0.005497800879682417</v>
       </c>
       <c r="H4">
-        <v>0.01135533401186041</v>
+        <v>0.008834302773363705</v>
       </c>
       <c r="I4" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0.0505797680927629</v>
       </c>
       <c r="C5">
-        <v>0.05181018488653797</v>
+        <v>0.07059608949622291</v>
       </c>
       <c r="D5">
         <v>0.12</v>
       </c>
       <c r="E5">
-        <v>2.316146917112817</v>
+        <v>1.699810865677204</v>
       </c>
       <c r="F5">
-        <v>0.117150173936334</v>
+        <v>0.0859760393875115</v>
       </c>
       <c r="G5">
         <v>0.05057976809307824</v>
       </c>
       <c r="H5">
-        <v>0.06657040584325577</v>
+        <v>0.03539627129443326</v>
       </c>
       <c r="I5" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0.01859256297481008</v>
       </c>
       <c r="C6">
-        <v>0.04770117265223589</v>
+        <v>0.07088224367916628</v>
       </c>
       <c r="D6">
         <v>0.12</v>
       </c>
       <c r="E6">
-        <v>2.515661425660471</v>
+        <v>1.692948667696737</v>
       </c>
       <c r="F6">
-        <v>0.04677259347989279</v>
+        <v>0.0314762547172724</v>
       </c>
       <c r="G6">
         <v>0.01859256297492599</v>
       </c>
       <c r="H6">
-        <v>0.0281800305049668</v>
+        <v>0.0128836917423464</v>
       </c>
       <c r="I6" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3264,25 +3171,25 @@
         <v>0.01859256297481008</v>
       </c>
       <c r="C7">
-        <v>0.06469555905163277</v>
+        <v>0.07287077570905091</v>
       </c>
       <c r="D7">
         <v>0.12</v>
       </c>
       <c r="E7">
-        <v>1.85484137951771</v>
+        <v>1.646750687533787</v>
       </c>
       <c r="F7">
-        <v>0.03448625515696662</v>
+        <v>0.03061731586178373</v>
       </c>
       <c r="G7">
         <v>0.01859256297492599</v>
       </c>
       <c r="H7">
-        <v>0.01589369218204063</v>
+        <v>0.01202475288685774</v>
       </c>
       <c r="I7" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3293,25 +3200,25 @@
         <v>0.01129548180727709</v>
       </c>
       <c r="C8">
-        <v>0.2144832259760696</v>
+        <v>0.2859915458182896</v>
       </c>
       <c r="D8">
         <v>0.12</v>
       </c>
       <c r="E8">
-        <v>0.5594843114369636</v>
+        <v>0.4195928227761124</v>
       </c>
       <c r="F8">
-        <v>0.006319644861293171</v>
+        <v>0.004739503096131617</v>
       </c>
       <c r="G8">
         <v>0.01129548180734751</v>
       </c>
       <c r="H8">
-        <v>0.00497583694605434</v>
+        <v>0.006555978711215895</v>
       </c>
       <c r="I8" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3322,54 +3229,54 @@
         <v>0.01129548180727709</v>
       </c>
       <c r="C9">
-        <v>0.189993640881627</v>
+        <v>0.2409868301034742</v>
       </c>
       <c r="D9">
         <v>0.12</v>
       </c>
       <c r="E9">
-        <v>0.6316000864195471</v>
+        <v>0.4979525227518646</v>
       </c>
       <c r="F9">
-        <v>0.007134227285626632</v>
+        <v>0.005624613661631418</v>
       </c>
       <c r="G9">
         <v>0.01129548180734751</v>
       </c>
       <c r="H9">
-        <v>0.00416125452172088</v>
+        <v>0.005670868145716094</v>
       </c>
       <c r="I9" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0.02249100359856058</v>
       </c>
       <c r="C10">
-        <v>0.1120818178495579</v>
+        <v>0.1573947913173104</v>
       </c>
       <c r="D10">
         <v>0.12</v>
       </c>
       <c r="E10">
-        <v>1.070646446518831</v>
+        <v>0.7624140481121647</v>
       </c>
       <c r="F10">
-        <v>0.02407991308144112</v>
+        <v>0.01714745709968383</v>
       </c>
       <c r="G10">
         <v>0.0224910035987008</v>
       </c>
       <c r="H10">
-        <v>0.001588909482740323</v>
+        <v>0.005343546499016964</v>
       </c>
       <c r="I10" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3380,199 +3287,199 @@
         <v>0.04498200719712115</v>
       </c>
       <c r="C11">
-        <v>0.1556175660677405</v>
+        <v>0.1956137069476524</v>
       </c>
       <c r="D11">
         <v>0.12</v>
       </c>
       <c r="E11">
-        <v>0.7711211724501835</v>
+        <v>0.6134539438594291</v>
       </c>
       <c r="F11">
-        <v>0.03468657812900666</v>
+        <v>0.02759438971778719</v>
       </c>
       <c r="G11">
         <v>0.04498200719740159</v>
       </c>
       <c r="H11">
-        <v>0.01029542906839494</v>
+        <v>0.0173876174796144</v>
       </c>
       <c r="I11" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>0.007297081167532987</v>
       </c>
       <c r="C12">
-        <v>0.06067006888567235</v>
+        <v>0.06327840262463671</v>
       </c>
       <c r="D12">
         <v>0.12</v>
       </c>
       <c r="E12">
-        <v>1.977911055715627</v>
+        <v>1.896381625051948</v>
       </c>
       <c r="F12">
-        <v>0.01443297751571779</v>
+        <v>0.01383805064262217</v>
       </c>
       <c r="G12">
         <v>0.007297081167111755</v>
       </c>
       <c r="H12">
-        <v>0.007135896348606034</v>
+        <v>0.006540969475510415</v>
       </c>
       <c r="I12" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.005497800879648141</v>
       </c>
       <c r="C13">
-        <v>0.03694532067208307</v>
+        <v>0.05500661444164982</v>
       </c>
       <c r="D13">
         <v>0.12</v>
       </c>
       <c r="E13">
-        <v>3.248043265481125</v>
+        <v>2.181555822296501</v>
       </c>
       <c r="F13">
-        <v>0.01785709512209735</v>
+        <v>0.01199375951882323</v>
       </c>
       <c r="G13">
         <v>0.005497800879682417</v>
       </c>
       <c r="H13">
-        <v>0.01235929424241493</v>
+        <v>0.006495958639140812</v>
       </c>
       <c r="I13" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0.09996001599360257</v>
       </c>
       <c r="C14">
-        <v>0.1282260148058714</v>
+        <v>0.1722147369141073</v>
       </c>
       <c r="D14">
         <v>0.12</v>
       </c>
       <c r="E14">
-        <v>0.9358475359440496</v>
+        <v>0.6968044788167601</v>
       </c>
       <c r="F14">
-        <v>0.09354733466054076</v>
+        <v>0.06965258684693725</v>
       </c>
       <c r="G14">
         <v>0.09996001599422578</v>
       </c>
       <c r="H14">
-        <v>0.006412681333685027</v>
+        <v>0.03030742914728854</v>
       </c>
       <c r="I14" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>0.005497800879648141</v>
       </c>
       <c r="C15">
-        <v>0.08358202127746187</v>
+        <v>0.1036987369168453</v>
       </c>
       <c r="D15">
         <v>0.12</v>
       </c>
       <c r="E15">
-        <v>1.435715458491291</v>
+        <v>1.157198280015951</v>
       </c>
       <c r="F15">
-        <v>0.007893277710617853</v>
+        <v>0.00636204572179901</v>
       </c>
       <c r="G15">
         <v>0.005497800879682417</v>
       </c>
       <c r="H15">
-        <v>0.002395476830935436</v>
+        <v>0.0008642448421165927</v>
       </c>
       <c r="I15" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0.04498200719712115</v>
       </c>
       <c r="C16">
-        <v>0.1217349660257986</v>
+        <v>0.179605306105785</v>
       </c>
       <c r="D16">
         <v>0.12</v>
       </c>
       <c r="E16">
-        <v>0.985748005832351</v>
+        <v>0.6681317083656853</v>
       </c>
       <c r="F16">
-        <v>0.04434092389289863</v>
+        <v>0.0300539053143301</v>
       </c>
       <c r="G16">
         <v>0.04498200719740159</v>
       </c>
       <c r="H16">
-        <v>0.0006410833045029582</v>
+        <v>0.01492810188307149</v>
       </c>
       <c r="I16" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0.06377449020391843</v>
       </c>
       <c r="C17">
-        <v>0.05563680009278063</v>
+        <v>0.06349041481209834</v>
       </c>
       <c r="D17">
         <v>0.12</v>
       </c>
       <c r="E17">
-        <v>2.156845825063384</v>
+        <v>1.890049078355266</v>
       </c>
       <c r="F17">
-        <v>0.1375517429418671</v>
+        <v>0.120536916432493</v>
       </c>
       <c r="G17">
         <v>0.06377449020431604</v>
       </c>
       <c r="H17">
-        <v>0.07377725273755111</v>
+        <v>0.05676242622817691</v>
       </c>
       <c r="I17" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3583,25 +3490,25 @@
         <v>0.03378648540583766</v>
       </c>
       <c r="C18">
-        <v>0.1777624223750275</v>
+        <v>0.2049949555736961</v>
       </c>
       <c r="D18">
         <v>0.12</v>
       </c>
       <c r="E18">
-        <v>0.6750583075810845</v>
+        <v>0.5853802580857154</v>
       </c>
       <c r="F18">
-        <v>0.02280784765717778</v>
+        <v>0.0197779415466785</v>
       </c>
       <c r="G18">
         <v>0.0337864854060483</v>
       </c>
       <c r="H18">
-        <v>0.01097863774887052</v>
+        <v>0.0140085438593698</v>
       </c>
       <c r="I18" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3612,54 +3519,54 @@
         <v>0.0899640143942423</v>
       </c>
       <c r="C19">
-        <v>0.1373249102743785</v>
+        <v>0.1884552982763563</v>
       </c>
       <c r="D19">
         <v>0.12</v>
       </c>
       <c r="E19">
-        <v>0.873840002955306</v>
+        <v>0.6367557776169739</v>
       </c>
       <c r="F19">
-        <v>0.07861415460413589</v>
+        <v>0.05728510594315039</v>
       </c>
       <c r="G19">
         <v>0.08996401438904929</v>
       </c>
       <c r="H19">
-        <v>0.0113498597849134</v>
+        <v>0.0326789084458989</v>
       </c>
       <c r="I19" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B20">
         <v>0.01129548180727709</v>
       </c>
       <c r="C20">
-        <v>0.1221898841733612</v>
+        <v>0.1396733541100288</v>
       </c>
       <c r="D20">
         <v>0.12</v>
       </c>
       <c r="E20">
-        <v>0.9820780239855681</v>
+        <v>0.8591474069239362</v>
       </c>
       <c r="F20">
-        <v>0.01109304445325562</v>
+        <v>0.009704483904678608</v>
       </c>
       <c r="G20">
         <v>0.01129548180734751</v>
       </c>
       <c r="H20">
-        <v>0.0002024373540918945</v>
+        <v>0.001590997902668903</v>
       </c>
       <c r="I20" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3670,228 +3577,228 @@
         <v>0.06377449020391843</v>
       </c>
       <c r="C21">
-        <v>0.07745530214105066</v>
+        <v>0.08383939575778916</v>
       </c>
       <c r="D21">
         <v>0.12</v>
       </c>
       <c r="E21">
-        <v>1.54928063906423</v>
+        <v>1.431308025485755</v>
       </c>
       <c r="F21">
-        <v>0.09880458293912221</v>
+        <v>0.09128093965013111</v>
       </c>
       <c r="G21">
         <v>0.06377449020431604</v>
       </c>
       <c r="H21">
-        <v>0.03503009273480617</v>
+        <v>0.02750644944581507</v>
       </c>
       <c r="I21" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22">
         <v>0.009096361455417834</v>
       </c>
       <c r="C22">
-        <v>0.01762469926214086</v>
+        <v>0.01679017434371363</v>
       </c>
       <c r="D22">
         <v>0.12</v>
       </c>
       <c r="E22">
-        <v>6.808626814856849</v>
+        <v>7.147037162537202</v>
       </c>
       <c r="F22">
-        <v>0.06193373052298814</v>
+        <v>0.06501203336574225</v>
       </c>
       <c r="G22">
         <v>0.009096361455474546</v>
       </c>
       <c r="H22">
-        <v>0.05283736906751359</v>
+        <v>0.05591567191026771</v>
       </c>
       <c r="I22" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>0.01009596161535386</v>
       </c>
       <c r="C23">
-        <v>0.04523816926953131</v>
+        <v>0.04596450331930595</v>
       </c>
       <c r="D23">
         <v>0.12</v>
       </c>
       <c r="E23">
-        <v>2.652627237964337</v>
+        <v>2.610710251047089</v>
       </c>
       <c r="F23">
-        <v>0.02678082277433008</v>
+        <v>0.02635763048338225</v>
       </c>
       <c r="G23">
         <v>0.0100959616154168</v>
       </c>
       <c r="H23">
-        <v>0.01668486115891327</v>
+        <v>0.01626166886796545</v>
       </c>
       <c r="I23" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24">
         <v>0.009096361455417834</v>
       </c>
       <c r="C24">
-        <v>0.0425423662168037</v>
+        <v>0.04326590760205494</v>
       </c>
       <c r="D24">
         <v>0.12</v>
       </c>
       <c r="E24">
-        <v>2.820717573358708</v>
+        <v>2.773546347477997</v>
       </c>
       <c r="F24">
-        <v>0.02565826661091988</v>
+        <v>0.02522918009001377</v>
       </c>
       <c r="G24">
         <v>0.009096361455474546</v>
       </c>
       <c r="H24">
-        <v>0.01656190515544533</v>
+        <v>0.01613281863453923</v>
       </c>
       <c r="I24" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>0.005497800879648141</v>
       </c>
       <c r="C25">
-        <v>0.03502611942537402</v>
+        <v>0.05448790929355872</v>
       </c>
       <c r="D25">
         <v>0.12</v>
       </c>
       <c r="E25">
-        <v>3.426014698992554</v>
+        <v>2.202323443050251</v>
       </c>
       <c r="F25">
-        <v>0.01883554662580872</v>
+        <v>0.01210793576247139</v>
       </c>
       <c r="G25">
         <v>0.005497800879682417</v>
       </c>
       <c r="H25">
-        <v>0.0133377457461263</v>
+        <v>0.006610134882788971</v>
       </c>
       <c r="I25" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26">
         <v>0.009096361455417834</v>
       </c>
       <c r="C26">
-        <v>0.01809404311665208</v>
+        <v>0.01577993773301148</v>
       </c>
       <c r="D26">
         <v>0.12</v>
       </c>
       <c r="E26">
-        <v>6.632016914426557</v>
+        <v>7.604592744935943</v>
       </c>
       <c r="F26">
-        <v>0.06032722303206885</v>
+        <v>0.06917412432918542</v>
       </c>
       <c r="G26">
         <v>0.009096361455474546</v>
       </c>
       <c r="H26">
-        <v>0.0512308615765943</v>
+        <v>0.06007776287371087</v>
       </c>
       <c r="I26" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0.009096361455417834</v>
       </c>
       <c r="C27">
-        <v>0.1215164053503871</v>
+        <v>0.1199080515509558</v>
       </c>
       <c r="D27">
         <v>0.12</v>
       </c>
       <c r="E27">
-        <v>0.9875209824877997</v>
+        <v>1.000766824644841</v>
       </c>
       <c r="F27">
-        <v>0.008982847801518371</v>
+        <v>0.009103336769560233</v>
       </c>
       <c r="G27">
         <v>0.009096361455474546</v>
       </c>
       <c r="H27">
-        <v>0.0001135136539561748</v>
+        <v>6.975314085687356E-06</v>
       </c>
       <c r="I27" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28">
         <v>0.009096361455417834</v>
       </c>
       <c r="C28">
-        <v>0.04551625614122628</v>
+        <v>0.0527875100871464</v>
       </c>
       <c r="D28">
         <v>0.12</v>
       </c>
       <c r="E28">
-        <v>2.636420702697254</v>
+        <v>2.273265016703632</v>
       </c>
       <c r="F28">
-        <v>0.02398183566028091</v>
+        <v>0.02067844027589269</v>
       </c>
       <c r="G28">
         <v>0.009096361455474546</v>
       </c>
       <c r="H28">
-        <v>0.01488547420480636</v>
+        <v>0.01158207882041815</v>
       </c>
       <c r="I28" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3902,141 +3809,141 @@
         <v>0.009096361455417834</v>
       </c>
       <c r="C29">
-        <v>0.0893857405791231</v>
+        <v>0.1109873177583198</v>
       </c>
       <c r="D29">
         <v>0.12</v>
       </c>
       <c r="E29">
-        <v>1.342496009123262</v>
+        <v>1.081204613497425</v>
       </c>
       <c r="F29">
-        <v>0.01221182895144111</v>
+        <v>0.00983502797163791</v>
       </c>
       <c r="G29">
         <v>0.009096361455474546</v>
       </c>
       <c r="H29">
-        <v>0.003115467495966567</v>
+        <v>0.0007386665161633645</v>
       </c>
       <c r="I29" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>0.1124550179928029</v>
       </c>
       <c r="C30">
-        <v>0.1246924739119454</v>
+        <v>0.1715950485483466</v>
       </c>
       <c r="D30">
         <v>0.12</v>
       </c>
       <c r="E30">
-        <v>0.9623676252084058</v>
+        <v>0.6993208779342501</v>
       </c>
       <c r="F30">
-        <v>0.1082230686085023</v>
+        <v>0.07864214191083881</v>
       </c>
       <c r="G30">
         <v>0.112455017993504</v>
       </c>
       <c r="H30">
-        <v>0.004231949385001738</v>
+        <v>0.03381287608266519</v>
       </c>
       <c r="I30" t="s">
-        <v>235</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>0.007297081167532987</v>
       </c>
       <c r="C31">
-        <v>0.04853638764815744</v>
+        <v>0.05523231249676754</v>
       </c>
       <c r="D31">
         <v>0.12</v>
       </c>
       <c r="E31">
-        <v>2.472371880451542</v>
+        <v>2.172641241610569</v>
       </c>
       <c r="F31">
-        <v>0.01804109828798106</v>
+        <v>0.01585393948796197</v>
       </c>
       <c r="G31">
         <v>0.007297081167578481</v>
       </c>
       <c r="H31">
-        <v>0.01074401712040258</v>
+        <v>0.008556858320383493</v>
       </c>
       <c r="I31" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>0.02479008396641344</v>
       </c>
       <c r="C32">
-        <v>0.04935812195542288</v>
+        <v>0.06594985582618719</v>
       </c>
       <c r="D32">
         <v>0.12</v>
       </c>
       <c r="E32">
-        <v>2.431210816902158</v>
+        <v>1.819564250697736</v>
       </c>
       <c r="F32">
-        <v>0.06026992029105709</v>
+        <v>0.04510715055708101</v>
       </c>
       <c r="G32">
         <v>0.02479008396656799</v>
       </c>
       <c r="H32">
-        <v>0.03547983632448909</v>
+        <v>0.02031706659051302</v>
       </c>
       <c r="I32" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>0.0235905637744902</v>
       </c>
       <c r="C33">
-        <v>0.08795103108520301</v>
+        <v>0.09983316117581224</v>
       </c>
       <c r="D33">
         <v>0.12</v>
       </c>
       <c r="E33">
-        <v>1.364395601954335</v>
+        <v>1.202005411695546</v>
       </c>
       <c r="F33">
-        <v>0.03218686146153769</v>
+        <v>0.02835598532188613</v>
       </c>
       <c r="G33">
         <v>0.02359056377463728</v>
       </c>
       <c r="H33">
-        <v>0.008596297686900414</v>
+        <v>0.004765421547248853</v>
       </c>
       <c r="I33" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -4055,63 +3962,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="B2">
-        <v>0.08745570542123857</v>
+        <v>0.1101112874923693</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B3">
-        <v>0.08051866170925626</v>
+        <v>0.08679860065202484</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="B4">
-        <v>0.01762469926214086</v>
+        <v>0.01577993773301148</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="B5">
-        <v>0.2144832259760696</v>
+        <v>0.2859915458182896</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="B6">
-        <v>0.05022194633741913</v>
+        <v>0.06773494527786549</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4124,18 +4031,18 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="B10">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
